--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45391</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>46199</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45544</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45903</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>46057</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45235</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44858</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>44596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>44633</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45058</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45006</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44754</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45015</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46150</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45404</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46055</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>46000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45719</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46218</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5110,24 +5110,24 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 841-2023</t>
+          <t>A 37224-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44992</v>
+        <v>46274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>23.9</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5164,58 +5164,58 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 841-2023 artfynd.xlsx", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37224-2026 artfynd.xlsx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 841-2023 karta.png", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37224-2026 karta.png", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 841-2023 georefererad karta.tif", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37224-2026 georefererad karta.tif", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 841-2023 FSC-klagomål.docx", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37224-2026 FSC-klagomål.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 841-2023 FSC-klagomål mail.docx", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37224-2026 FSC-klagomål mail.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 841-2023 tillsynsbegäran.docx", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37224-2026 tillsynsbegäran.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 841-2023 tillsynsbegäran mail.docx", "S 841-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37224-2026 tillsynsbegäran mail.docx", "A 37224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 3667-2023</t>
+          <t>S 841-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45217</v>
+        <v>44992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>186.4</v>
+        <v>23.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5257,10 +5257,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5281,46 +5281,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 3667-2023 artfynd.xlsx", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 841-2023 artfynd.xlsx", "S 841-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 3667-2023 karta.png", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 841-2023 karta.png", "S 841-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 3667-2023 georefererad karta.tif", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 841-2023 georefererad karta.tif", "S 841-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 3667-2023 FSC-klagomål.docx", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 841-2023 FSC-klagomål.docx", "S 841-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 3667-2023 FSC-klagomål mail.docx", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 841-2023 FSC-klagomål mail.docx", "S 841-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 3667-2023 tillsynsbegäran.docx", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 841-2023 tillsynsbegäran.docx", "S 841-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 3667-2023 tillsynsbegäran mail.docx", "S 3667-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 841-2023 tillsynsbegäran mail.docx", "S 841-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 5988-2022</t>
+          <t>S 3667-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44859</v>
+        <v>45217</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,23 +5350,23 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>27.8</v>
+        <v>186.4</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -5374,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5390,42 +5390,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 5988-2022 artfynd.xlsx", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 3667-2023 artfynd.xlsx", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 5988-2022 karta.png", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 3667-2023 karta.png", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 5988-2022 georefererad karta.tif", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 3667-2023 georefererad karta.tif", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 5988-2022 FSC-klagomål.docx", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 3667-2023 FSC-klagomål.docx", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 5988-2022 FSC-klagomål mail.docx", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 3667-2023 FSC-klagomål mail.docx", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 5988-2022 tillsynsbegäran.docx", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 3667-2023 tillsynsbegäran.docx", "S 3667-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 5988-2022 tillsynsbegäran mail.docx", "S 5988-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 3667-2023 tillsynsbegäran mail.docx", "S 3667-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S 2025-2022</t>
+          <t>S 5988-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44665</v>
+        <v>44859</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>27.8</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5491,63 +5491,63 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 2025-2022 artfynd.xlsx", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 5988-2022 artfynd.xlsx", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 2025-2022 karta.png", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 5988-2022 karta.png", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 2025-2022 georefererad karta.tif", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 5988-2022 georefererad karta.tif", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 2025-2022 FSC-klagomål.docx", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 5988-2022 FSC-klagomål.docx", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 2025-2022 FSC-klagomål mail.docx", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 5988-2022 FSC-klagomål mail.docx", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 2025-2022 tillsynsbegäran.docx", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 5988-2022 tillsynsbegäran.docx", "S 5988-2022")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 2025-2022 tillsynsbegäran mail.docx", "S 2025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 5988-2022 tillsynsbegäran mail.docx", "S 5988-2022")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55629-2022</t>
+          <t>S 2025-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44883</v>
+        <v>44665</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5559,19 +5559,14 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5595,20 +5590,52 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/S 2025-2022 artfynd.xlsx", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/S 2025-2022 karta.png", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/S 2025-2022 georefererad karta.tif", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/S 2025-2022 FSC-klagomål.docx", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/S 2025-2022 FSC-klagomål mail.docx", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/S 2025-2022 tillsynsbegäran.docx", "S 2025-2022")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/S 2025-2022 tillsynsbegäran mail.docx", "S 2025-2022")</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55637-2022</t>
+          <t>A 55629-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5625,7 +5652,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5643,7 +5670,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5686,7 +5713,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5791-2022</t>
+          <t>A 55637-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5700,10 +5727,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44596</v>
+        <v>44883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5721,7 +5748,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5764,7 +5791,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58633-2021</t>
+          <t>A 5791-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5778,10 +5805,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44489</v>
+        <v>44596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5793,8 +5820,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5837,7 +5869,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19097-2022</t>
+          <t>A 58633-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5851,10 +5883,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44691</v>
+        <v>44489</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5867,7 +5899,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5910,7 +5942,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20010-2022</t>
+          <t>A 19097-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5924,10 +5956,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44697</v>
+        <v>44691</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5940,7 +5972,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5983,7 +6015,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19999-2022</t>
+          <t>A 20010-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6000,7 +6032,7 @@
         <v>44697</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6013,7 +6045,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6056,7 +6088,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 69392-2021</t>
+          <t>A 19999-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6070,10 +6102,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44531</v>
+        <v>44697</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6086,7 +6118,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6129,7 +6161,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57952-2021</t>
+          <t>A 69392-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6143,10 +6175,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44487</v>
+        <v>44531</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6158,13 +6190,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6207,7 +6234,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2045-2022</t>
+          <t>A 57952-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6221,10 +6248,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44575</v>
+        <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6238,11 +6265,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6285,7 +6312,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53582-2022</t>
+          <t>A 2045-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6299,10 +6326,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44875</v>
+        <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6316,11 +6343,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6363,7 +6390,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10055-2022</t>
+          <t>A 53582-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6377,10 +6404,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44621</v>
+        <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6392,8 +6419,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6436,7 +6468,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 7839-2022</t>
+          <t>A 10055-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6450,10 +6482,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44608</v>
+        <v>44621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6465,13 +6497,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6514,7 +6541,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2046-2022</t>
+          <t>A 7839-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6528,10 +6555,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44575</v>
+        <v>44608</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6545,11 +6572,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6592,7 +6619,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41272-2022</t>
+          <t>A 2046-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6606,10 +6633,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44825</v>
+        <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6623,11 +6650,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6670,7 +6697,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32455-2022</t>
+          <t>A 41272-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6684,10 +6711,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44782</v>
+        <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6699,8 +6726,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6743,7 +6775,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41268-2022</t>
+          <t>A 32455-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6757,10 +6789,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44825</v>
+        <v>44782</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6772,13 +6804,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6821,7 +6848,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54516-2022</t>
+          <t>A 41268-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6835,10 +6862,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44880</v>
+        <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6850,8 +6877,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6894,7 +6926,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20690-2022</t>
+          <t>A 54516-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6908,10 +6940,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44700</v>
+        <v>44880</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6923,13 +6955,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6972,7 +6999,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17425-2022</t>
+          <t>A 20690-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6986,10 +7013,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44679</v>
+        <v>44700</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7001,8 +7028,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7045,7 +7077,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39056-2022</t>
+          <t>A 17425-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7059,10 +7091,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44816</v>
+        <v>44679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7075,7 +7107,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7118,7 +7150,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 243-2025</t>
+          <t>A 39056-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7128,14 +7160,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45660</v>
+        <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7148,7 +7180,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7191,7 +7223,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3198-2023</t>
+          <t>A 243-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7201,14 +7233,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44944</v>
+        <v>45660</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7221,7 +7253,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7264,7 +7296,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25393-2023</t>
+          <t>A 3198-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7278,10 +7310,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45079</v>
+        <v>44944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7294,7 +7326,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7337,7 +7369,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53868-2022</t>
+          <t>A 25393-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7351,10 +7383,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44880</v>
+        <v>45079</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7367,7 +7399,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7410,7 +7442,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34051-2024</t>
+          <t>A 53868-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7424,10 +7456,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45523</v>
+        <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7440,7 +7472,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7483,7 +7515,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28844-2023</t>
+          <t>A 34051-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7497,10 +7529,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45104</v>
+        <v>45523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7513,7 +7545,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7556,7 +7588,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37967-2024</t>
+          <t>A 28844-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7570,10 +7602,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45544</v>
+        <v>45104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7586,7 +7618,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7629,7 +7661,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4623-2024</t>
+          <t>A 37967-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7643,10 +7675,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45328</v>
+        <v>45544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7659,7 +7691,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7702,7 +7734,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 593-2023</t>
+          <t>A 4623-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7716,10 +7748,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44930</v>
+        <v>45328</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7732,7 +7764,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7775,7 +7807,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33331-2024</t>
+          <t>A 593-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7789,10 +7821,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45519</v>
+        <v>44930</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7804,13 +7836,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7853,7 +7880,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 217-2023</t>
+          <t>A 33331-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7867,10 +7894,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44928</v>
+        <v>45519</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7882,8 +7909,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7926,7 +7958,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15070-2024</t>
+          <t>A 217-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7940,10 +7972,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45399</v>
+        <v>44928</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7955,13 +7987,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8004,7 +8031,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38724-2023</t>
+          <t>A 15070-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8018,10 +8045,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45163</v>
+        <v>45399</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8033,8 +8060,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8077,7 +8109,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5256-2022</t>
+          <t>A 38724-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8091,10 +8123,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44593</v>
+        <v>45163</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8107,7 +8139,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8150,7 +8182,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58642-2021</t>
+          <t>A 5256-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8164,10 +8196,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44489</v>
+        <v>44593</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8180,7 +8212,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8223,7 +8255,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25069-2023</t>
+          <t>A 58642-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8237,10 +8269,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45086</v>
+        <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8253,7 +8285,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8296,7 +8328,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18214-2023</t>
+          <t>A 25069-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8310,10 +8342,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45040</v>
+        <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8326,7 +8358,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8369,7 +8401,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60791-2023</t>
+          <t>A 18214-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8383,10 +8415,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45260</v>
+        <v>45040</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8399,7 +8431,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8442,7 +8474,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23681-2023</t>
+          <t>A 60791-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8456,10 +8488,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45077</v>
+        <v>45260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8472,7 +8504,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8515,7 +8547,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4324-2024</t>
+          <t>A 23681-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8529,10 +8561,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45324</v>
+        <v>45077</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8545,7 +8577,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8588,7 +8620,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28490-2023</t>
+          <t>A 4324-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8602,10 +8634,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45103</v>
+        <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8618,7 +8650,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8661,7 +8693,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44891-2022</t>
+          <t>A 28490-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8675,10 +8707,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44841</v>
+        <v>45103</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8691,7 +8723,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8734,7 +8766,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17856-2024</t>
+          <t>A 44891-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8748,10 +8780,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45419</v>
+        <v>44841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8763,13 +8795,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8812,7 +8839,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13994-2025</t>
+          <t>A 17856-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8826,10 +8853,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45739</v>
+        <v>45419</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8841,8 +8868,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8885,7 +8917,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39238-2022</t>
+          <t>A 13994-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8899,10 +8931,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44817</v>
+        <v>45739</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8915,7 +8947,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8958,7 +8990,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11497-2023</t>
+          <t>A 39238-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8972,10 +9004,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44991</v>
+        <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8988,7 +9020,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9031,7 +9063,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46260-2024</t>
+          <t>A 11497-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9045,10 +9077,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45581</v>
+        <v>44991</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9060,13 +9092,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9109,7 +9136,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37068-2023</t>
+          <t>A 46260-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9123,10 +9150,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45155</v>
+        <v>45581</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9138,8 +9165,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9182,7 +9214,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 39244-2022</t>
+          <t>A 37068-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9196,10 +9228,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44817</v>
+        <v>45155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9212,7 +9244,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9255,7 +9287,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20717-2023</t>
+          <t>A 39244-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9269,10 +9301,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45055</v>
+        <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9285,7 +9317,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9328,7 +9360,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 55588-2021</t>
+          <t>A 20717-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9342,10 +9374,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44475</v>
+        <v>45055</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9358,7 +9390,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9401,7 +9433,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52286-2023</t>
+          <t>A 55588-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9415,10 +9447,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45224</v>
+        <v>44475</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9431,7 +9463,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9474,7 +9506,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 46619-2024</t>
+          <t>A 52286-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9488,10 +9520,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45583</v>
+        <v>45224</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9504,7 +9536,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9547,7 +9579,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24333-2022</t>
+          <t>A 46619-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9561,10 +9593,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44726</v>
+        <v>45583</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9577,7 +9609,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9620,7 +9652,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56089-2021</t>
+          <t>A 24333-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9634,10 +9666,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44477</v>
+        <v>44726</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9650,7 +9682,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>20.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9693,7 +9725,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52851-2024</t>
+          <t>A 56089-2021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9707,10 +9739,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45610</v>
+        <v>44477</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9723,7 +9755,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>20.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9766,7 +9798,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54348-2022</t>
+          <t>A 52851-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9780,10 +9812,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44882</v>
+        <v>45610</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9796,7 +9828,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.8</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9839,7 +9871,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38156-2022</t>
+          <t>A 54348-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9853,10 +9885,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44812</v>
+        <v>44882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9869,7 +9901,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9912,7 +9944,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40710-2023</t>
+          <t>A 38156-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9926,10 +9958,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45170</v>
+        <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9942,7 +9974,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9985,7 +10017,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61060-2025</t>
+          <t>A 40710-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9999,10 +10031,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>45170</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10014,13 +10046,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10063,7 +10090,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43855-2022</t>
+          <t>A 61060-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10077,10 +10104,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44838</v>
+        <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10098,7 +10125,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10141,7 +10168,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20088-2026</t>
+          <t>A 43855-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10155,10 +10182,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46136</v>
+        <v>44838</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10176,7 +10203,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10219,7 +10246,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55833-2023</t>
+          <t>A 20088-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10229,14 +10256,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45239</v>
+        <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10248,8 +10275,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10292,7 +10324,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20128-2023</t>
+          <t>A 55833-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10302,14 +10334,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45055</v>
+        <v>45239</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10322,7 +10354,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10365,7 +10397,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2252-2025</t>
+          <t>A 20128-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10379,10 +10411,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45673</v>
+        <v>45055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10395,7 +10427,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10438,7 +10470,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42627-2025</t>
+          <t>A 2252-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10452,10 +10484,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45905</v>
+        <v>45673</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10468,7 +10500,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10511,7 +10543,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61682-2023</t>
+          <t>A 42627-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10525,10 +10557,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45264</v>
+        <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10541,7 +10573,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10584,7 +10616,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11676-2023</t>
+          <t>A 61682-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10598,10 +10630,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44992</v>
+        <v>45264</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10613,13 +10645,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10662,7 +10689,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51844-2023</t>
+          <t>A 11676-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10676,10 +10703,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45223</v>
+        <v>44992</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10691,8 +10718,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10735,7 +10767,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34479-2025</t>
+          <t>A 51844-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10749,10 +10781,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45847</v>
+        <v>45223</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10765,7 +10797,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10808,7 +10840,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20627-2026</t>
+          <t>A 34479-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10822,10 +10854,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46141</v>
+        <v>45847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10838,7 +10870,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10881,7 +10913,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20629-2026</t>
+          <t>A 20627-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10898,7 +10930,7 @@
         <v>46141</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10911,7 +10943,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10954,7 +10986,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28847-2023</t>
+          <t>A 20629-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10968,10 +11000,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45104</v>
+        <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10984,7 +11016,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11027,7 +11059,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15442-2022</t>
+          <t>A 28847-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11041,10 +11073,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44659</v>
+        <v>45104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11057,7 +11089,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11100,7 +11132,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2755-2023</t>
+          <t>A 15442-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11114,10 +11146,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44944</v>
+        <v>44659</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11129,13 +11161,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11178,7 +11205,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 49370-2023</t>
+          <t>A 2755-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11192,10 +11219,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45211</v>
+        <v>44944</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11207,8 +11234,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11251,7 +11283,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45096-2025</t>
+          <t>A 49370-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11265,10 +11297,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45919</v>
+        <v>45211</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11281,7 +11313,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11324,7 +11356,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46728-2023</t>
+          <t>A 45096-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11334,14 +11366,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45198</v>
+        <v>45919</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11354,7 +11386,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11397,7 +11429,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3498-2024</t>
+          <t>A 46728-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11407,14 +11439,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45320</v>
+        <v>45198</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11427,7 +11459,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11470,7 +11502,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41294-2022</t>
+          <t>A 3498-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11484,10 +11516,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44825</v>
+        <v>45320</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11500,7 +11532,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11543,7 +11575,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39097-2024</t>
+          <t>A 41294-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11557,10 +11589,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45548</v>
+        <v>44825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11573,7 +11605,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11616,7 +11648,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 8712-2023</t>
+          <t>A 39097-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11630,10 +11662,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44978</v>
+        <v>45548</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11646,7 +11678,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11689,7 +11721,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 49073-2024</t>
+          <t>A 8712-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11703,10 +11735,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45594</v>
+        <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11719,7 +11751,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11762,7 +11794,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 21602-2026</t>
+          <t>A 49073-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11776,10 +11808,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46149</v>
+        <v>45594</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11792,7 +11824,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11835,7 +11867,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21609-2026</t>
+          <t>A 21602-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11852,7 +11884,7 @@
         <v>46149</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11865,7 +11897,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11908,7 +11940,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40092-2025</t>
+          <t>A 21609-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11922,10 +11954,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45894</v>
+        <v>46149</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11938,7 +11970,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11981,7 +12013,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7661-2025</t>
+          <t>A 40092-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11995,10 +12027,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45706</v>
+        <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12054,7 +12086,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21608-2026</t>
+          <t>A 7661-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12068,10 +12100,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46149</v>
+        <v>45706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12084,7 +12116,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12127,7 +12159,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21599-2026</t>
+          <t>A 21608-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12144,7 +12176,7 @@
         <v>46149</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12157,7 +12189,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12200,7 +12232,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21607-2026</t>
+          <t>A 21599-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12217,7 +12249,7 @@
         <v>46149</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12230,7 +12262,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12273,7 +12305,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3183-2023</t>
+          <t>A 21607-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12287,10 +12319,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44944</v>
+        <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12303,7 +12335,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12346,7 +12378,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 51396-2025</t>
+          <t>A 3183-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12360,10 +12392,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45950</v>
+        <v>44944</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12376,7 +12408,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12419,7 +12451,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 48965-2023</t>
+          <t>A 51396-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12433,10 +12465,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45209</v>
+        <v>45950</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12449,7 +12481,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12492,7 +12524,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9270-2022</t>
+          <t>A 48965-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12506,10 +12538,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44616</v>
+        <v>45209</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12522,7 +12554,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12565,7 +12597,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36842-2024</t>
+          <t>A 9270-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12579,10 +12611,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45538</v>
+        <v>44616</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12594,13 +12626,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12643,7 +12670,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21778-2026</t>
+          <t>A 36842-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12657,10 +12684,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46150</v>
+        <v>45538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12672,8 +12699,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12716,7 +12748,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4321-2024</t>
+          <t>A 21778-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12730,10 +12762,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45324</v>
+        <v>46150</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12789,7 +12821,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8500-2023</t>
+          <t>A 4321-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12803,10 +12835,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44977</v>
+        <v>45324</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12819,7 +12851,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12862,7 +12894,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 63499-2025</t>
+          <t>A 8500-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12876,10 +12908,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46013</v>
+        <v>44977</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12892,7 +12924,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12935,7 +12967,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 55291-2023</t>
+          <t>A 63499-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12949,10 +12981,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45237</v>
+        <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12965,7 +12997,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13008,7 +13040,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 55696-2025</t>
+          <t>A 55291-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13022,10 +13054,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45972</v>
+        <v>45237</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13038,7 +13070,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13081,7 +13113,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33462-2025</t>
+          <t>A 55696-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13095,10 +13127,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45841</v>
+        <v>45972</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13111,7 +13143,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13154,7 +13186,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 69041-2021</t>
+          <t>A 33462-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13164,14 +13196,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44529</v>
+        <v>45841</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13184,7 +13216,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13227,7 +13259,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57687-2025</t>
+          <t>A 69041-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13237,14 +13269,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45981</v>
+        <v>44529</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13256,13 +13288,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13305,7 +13332,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 23260-2023</t>
+          <t>A 57687-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13319,10 +13346,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45075</v>
+        <v>45981</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13334,8 +13361,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13378,7 +13410,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55586-2021</t>
+          <t>A 23260-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13392,10 +13424,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44475</v>
+        <v>45075</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13408,7 +13440,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13451,7 +13483,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23220-2026</t>
+          <t>A 55586-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13465,10 +13497,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46162</v>
+        <v>44475</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13524,7 +13556,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10695-2023</t>
+          <t>A 23220-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13538,10 +13570,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44988</v>
+        <v>46162</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13554,7 +13586,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13597,7 +13629,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 42006-2025</t>
+          <t>A 10695-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13611,10 +13643,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45903</v>
+        <v>44988</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13627,7 +13659,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13670,7 +13702,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14614-2023</t>
+          <t>A 42006-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13684,10 +13716,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45013</v>
+        <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13700,7 +13732,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13743,7 +13775,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8017-2022</t>
+          <t>A 14614-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13757,10 +13789,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44609</v>
+        <v>45013</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13773,7 +13805,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13816,7 +13848,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50781-2025</t>
+          <t>A 8017-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13830,10 +13862,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45946</v>
+        <v>44609</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13889,7 +13921,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 317-2026</t>
+          <t>A 50781-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13903,10 +13935,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46027</v>
+        <v>45946</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13919,7 +13951,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13962,7 +13994,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 13995-2025</t>
+          <t>A 317-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13976,10 +14008,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45739</v>
+        <v>46027</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13992,7 +14024,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14035,7 +14067,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 42275-2024</t>
+          <t>A 13995-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14049,10 +14081,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45562</v>
+        <v>45739</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14064,13 +14096,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14113,7 +14140,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24034-2023</t>
+          <t>A 42275-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14127,10 +14154,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45078</v>
+        <v>45562</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14142,8 +14169,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14186,7 +14218,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5196-2022</t>
+          <t>A 24034-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14200,10 +14232,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44593</v>
+        <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14216,7 +14248,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14259,7 +14291,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 2806-2026</t>
+          <t>A 5196-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14273,10 +14305,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46038</v>
+        <v>44593</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14289,7 +14321,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.9</v>
+        <v>5.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14332,7 +14364,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 45641-2022</t>
+          <t>A 2806-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14342,14 +14374,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44845</v>
+        <v>46038</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14362,7 +14394,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>7.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14405,7 +14437,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21636-2024</t>
+          <t>A 45641-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14415,14 +14447,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45442</v>
+        <v>44845</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14435,7 +14467,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14478,7 +14510,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 4968-2026</t>
+          <t>A 21636-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14492,10 +14524,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46049</v>
+        <v>45442</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14508,7 +14540,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14551,7 +14583,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25423-2026</t>
+          <t>A 4968-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14565,10 +14597,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46177</v>
+        <v>46049</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14581,7 +14613,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14624,7 +14656,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25424-2026</t>
+          <t>A 25423-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14641,7 +14673,7 @@
         <v>46177</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14654,7 +14686,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14697,7 +14729,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 60783-2023</t>
+          <t>A 25424-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14711,10 +14743,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45260</v>
+        <v>46177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14727,7 +14759,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14770,7 +14802,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14619-2023</t>
+          <t>A 60783-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14784,10 +14816,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45013</v>
+        <v>45260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14800,7 +14832,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14843,7 +14875,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25721-2026</t>
+          <t>A 14619-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14857,10 +14889,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46178</v>
+        <v>45013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14873,7 +14905,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14916,7 +14948,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 27454-2024</t>
+          <t>A 25721-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14930,10 +14962,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45474</v>
+        <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14946,7 +14978,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14989,7 +15021,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 11335-2023</t>
+          <t>A 27454-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15003,10 +15035,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44993</v>
+        <v>45474</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15019,7 +15051,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15062,7 +15094,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6447-2026</t>
+          <t>A 11335-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15076,10 +15108,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46055</v>
+        <v>44993</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15092,7 +15124,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15135,7 +15167,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13363-2023</t>
+          <t>A 6447-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15149,10 +15181,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45005</v>
+        <v>46055</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15164,13 +15196,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15213,7 +15240,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 5151-2022</t>
+          <t>A 13363-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15227,10 +15254,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44593</v>
+        <v>45005</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15242,8 +15269,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15286,7 +15318,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53289-2025</t>
+          <t>A 5151-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15300,10 +15332,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45958</v>
+        <v>44593</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15316,7 +15348,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15359,7 +15391,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53290-2025</t>
+          <t>A 53289-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15376,7 +15408,7 @@
         <v>45958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15389,7 +15421,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15432,7 +15464,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 23741-2023</t>
+          <t>A 53290-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15446,10 +15478,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45077</v>
+        <v>45958</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15462,7 +15494,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15505,7 +15537,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9488-2026</t>
+          <t>A 23741-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15519,10 +15551,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46071</v>
+        <v>45077</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15535,7 +15567,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15578,7 +15610,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 47870-2022</t>
+          <t>A 9488-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15592,10 +15624,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44855</v>
+        <v>46071</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15608,7 +15640,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15651,7 +15683,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27813-2023</t>
+          <t>A 47870-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15665,10 +15697,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45098</v>
+        <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15681,7 +15713,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15724,7 +15756,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58387-2022</t>
+          <t>A 27813-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15738,10 +15770,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44901</v>
+        <v>45098</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15753,13 +15785,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15802,7 +15829,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27452-2024</t>
+          <t>A 58387-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15816,10 +15843,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45474</v>
+        <v>44901</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15829,6 +15856,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -15875,7 +15907,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 45596-2024</t>
+          <t>A 27452-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15889,10 +15921,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45579</v>
+        <v>45474</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15905,7 +15937,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15948,7 +15980,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 38323-2023</t>
+          <t>A 45596-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15962,10 +15994,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45161</v>
+        <v>45579</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15978,7 +16010,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16021,7 +16053,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38325-2023</t>
+          <t>A 38323-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16038,7 +16070,7 @@
         <v>45161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16051,7 +16083,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16094,7 +16126,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 21654-2024</t>
+          <t>A 38325-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16108,10 +16140,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45442</v>
+        <v>45161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16124,7 +16156,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16167,7 +16199,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 14774-2026</t>
+          <t>A 21654-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16181,10 +16213,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46101</v>
+        <v>45442</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16197,7 +16229,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16240,7 +16272,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 1280-2023</t>
+          <t>A 14774-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16254,10 +16286,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44936</v>
+        <v>46101</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16270,7 +16302,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16313,7 +16345,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 20591-2023</t>
+          <t>A 1280-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16327,10 +16359,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45055</v>
+        <v>44936</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16343,7 +16375,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16386,7 +16418,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 52877-2022</t>
+          <t>A 20591-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16400,10 +16432,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44875</v>
+        <v>45055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16416,7 +16448,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16459,7 +16491,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29338-2026</t>
+          <t>A 52877-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16473,10 +16505,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46202</v>
+        <v>44875</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16489,7 +16521,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16532,7 +16564,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 11705-2023</t>
+          <t>A 29338-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16546,10 +16578,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44992</v>
+        <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16562,7 +16594,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16605,7 +16637,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 64224-2023</t>
+          <t>A 11705-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16619,10 +16651,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45279</v>
+        <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16635,7 +16667,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16678,7 +16710,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20002-2022</t>
+          <t>A 64224-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16692,10 +16724,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44697</v>
+        <v>45279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16751,7 +16783,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 47856-2024</t>
+          <t>A 20002-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16765,10 +16797,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45588</v>
+        <v>44697</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16781,7 +16813,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16824,7 +16856,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 49686-2023</t>
+          <t>A 47856-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16838,10 +16870,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45212</v>
+        <v>45588</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16854,7 +16886,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16897,7 +16929,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 68856-2021</t>
+          <t>A 49686-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16911,10 +16943,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44530</v>
+        <v>45212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16927,7 +16959,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16970,7 +17002,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 46835-2023</t>
+          <t>A 68856-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16984,10 +17016,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45199</v>
+        <v>44530</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17000,7 +17032,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17043,7 +17075,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 5557-2022</t>
+          <t>A 46835-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17057,10 +17089,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44593</v>
+        <v>45199</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17073,7 +17105,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17116,7 +17148,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33181-2026</t>
+          <t>A 5557-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17130,10 +17162,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46245</v>
+        <v>44593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17146,7 +17178,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17189,7 +17221,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 46253-2024</t>
+          <t>A 33181-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17203,10 +17235,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45581</v>
+        <v>46245</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17218,13 +17250,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17267,7 +17294,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 39530-2023</t>
+          <t>A 46253-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17281,10 +17308,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45167</v>
+        <v>45581</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17296,8 +17323,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17340,7 +17372,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 22976-2023</t>
+          <t>A 39530-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17354,10 +17386,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45072</v>
+        <v>45167</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17370,7 +17402,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17413,7 +17445,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 23978-2022</t>
+          <t>A 22976-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17427,10 +17459,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44722</v>
+        <v>45072</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17443,7 +17475,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17486,7 +17518,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15812-2024</t>
+          <t>A 23978-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17500,10 +17532,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45404</v>
+        <v>44722</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17515,13 +17547,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17564,7 +17591,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38945-2023</t>
+          <t>A 15812-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17578,10 +17605,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45163</v>
+        <v>45404</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17593,8 +17620,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17637,7 +17669,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 55587-2021</t>
+          <t>A 38945-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17651,10 +17683,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44475</v>
+        <v>45163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17667,7 +17699,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17710,7 +17742,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 30240-2026</t>
+          <t>A 55587-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17724,10 +17756,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46206</v>
+        <v>44475</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17739,13 +17771,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>10.9</v>
+        <v>2.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17788,7 +17815,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 23874-2022</t>
+          <t>A 30240-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17802,10 +17829,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44722</v>
+        <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17817,8 +17844,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>7.8</v>
+        <v>10.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17861,7 +17893,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 33783-2026</t>
+          <t>A 23874-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17875,10 +17907,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46251</v>
+        <v>44722</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17891,7 +17923,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17934,7 +17966,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 30215-2026</t>
+          <t>A 33783-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17948,10 +17980,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17963,13 +17995,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18012,7 +18039,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9142-2025</t>
+          <t>A 30215-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18026,10 +18053,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45714</v>
+        <v>46206</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18041,8 +18068,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18085,7 +18117,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 30422-2026</t>
+          <t>A 9142-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18099,10 +18131,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46209</v>
+        <v>45714</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18114,13 +18146,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18163,7 +18190,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28247-2023</t>
+          <t>A 30422-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18177,10 +18204,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45099</v>
+        <v>46209</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18192,8 +18219,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18236,7 +18268,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 56759-2023</t>
+          <t>A 28247-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18250,10 +18282,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45238</v>
+        <v>45099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18266,7 +18298,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18309,7 +18341,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 4301-2024</t>
+          <t>A 56759-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18323,10 +18355,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45324</v>
+        <v>45238</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18338,13 +18370,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18387,7 +18414,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34199-2026</t>
+          <t>A 4301-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18401,10 +18428,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46253</v>
+        <v>45324</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18416,8 +18443,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18460,7 +18492,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 30353-2026</t>
+          <t>A 34199-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18474,10 +18506,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46209</v>
+        <v>46253</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18489,13 +18521,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18538,7 +18565,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 30346-2026</t>
+          <t>A 30353-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18555,7 +18582,7 @@
         <v>46209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18573,7 +18600,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18616,7 +18643,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 22202-2023</t>
+          <t>A 30346-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18630,10 +18657,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45069</v>
+        <v>46209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18645,8 +18672,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18689,7 +18721,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 30356-2026</t>
+          <t>A 22202-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18703,10 +18735,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46209</v>
+        <v>45069</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18718,13 +18750,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18767,7 +18794,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 20012-2022</t>
+          <t>A 30356-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18781,10 +18808,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44697</v>
+        <v>46209</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18796,8 +18823,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>17.2</v>
+        <v>2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18840,7 +18872,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 16418-2025</t>
+          <t>A 20012-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18854,10 +18886,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45751</v>
+        <v>44697</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18870,7 +18902,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.8</v>
+        <v>17.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18913,7 +18945,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 31120-2026</t>
+          <t>A 16418-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18927,10 +18959,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46216</v>
+        <v>45751</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18943,7 +18975,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18986,7 +19018,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23341-2026</t>
+          <t>A 31120-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19000,10 +19032,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46162</v>
+        <v>46216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19016,7 +19048,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19059,7 +19091,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 63720-2023</t>
+          <t>A 23341-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19073,10 +19105,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45275</v>
+        <v>46162</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19089,7 +19121,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19132,7 +19164,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 14278-2024</t>
+          <t>A 63720-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19146,10 +19178,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45393</v>
+        <v>45275</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19162,7 +19194,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19205,7 +19237,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31119-2026</t>
+          <t>A 14278-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19219,10 +19251,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46216</v>
+        <v>45393</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19235,7 +19267,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19278,7 +19310,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31121-2026</t>
+          <t>A 31119-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19295,7 +19327,7 @@
         <v>46216</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19351,7 +19383,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 47869-2022</t>
+          <t>A 31121-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19365,10 +19397,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44855</v>
+        <v>46216</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19381,7 +19413,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19424,7 +19456,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 29500-2026</t>
+          <t>A 47869-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19438,10 +19470,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46198</v>
+        <v>44855</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19453,13 +19485,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19502,7 +19529,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 6615-2024</t>
+          <t>A 29500-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19516,10 +19543,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45341</v>
+        <v>46198</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19531,8 +19558,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19575,7 +19607,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 24647-2023</t>
+          <t>A 6615-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19589,10 +19621,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45084</v>
+        <v>45341</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19604,13 +19636,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>11.6</v>
+        <v>0.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19653,7 +19680,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 13420-2023</t>
+          <t>A 24647-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19667,10 +19694,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19688,7 +19715,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19731,7 +19758,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 35635-2026</t>
+          <t>A 13420-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19745,10 +19772,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46265</v>
+        <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19760,8 +19787,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19804,7 +19836,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 42281-2024</t>
+          <t>A 35635-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19818,10 +19850,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45562</v>
+        <v>46265</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19833,13 +19865,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19882,7 +19909,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 42284-2024</t>
+          <t>A 42281-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19899,7 +19926,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19917,7 +19944,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19960,7 +19987,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 3489-2024</t>
+          <t>A 42284-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19974,10 +20001,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45320</v>
+        <v>45562</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19989,8 +20016,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20033,7 +20065,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 36480-2026</t>
+          <t>A 3489-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20047,10 +20079,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46269</v>
+        <v>45320</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20106,7 +20138,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 36475-2026</t>
+          <t>A 36480-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20123,7 +20155,7 @@
         <v>46269</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20136,7 +20168,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20179,7 +20211,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30520-2026</t>
+          <t>A 36475-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20193,10 +20225,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46210</v>
+        <v>46269</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20208,13 +20240,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20257,7 +20284,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 37224-2026</t>
+          <t>A 30520-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20271,10 +20298,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46274</v>
+        <v>46210</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20286,8 +20313,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20347,7 +20379,7 @@
         <v>45554</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20425,7 +20457,7 @@
         <v>45349</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20503,7 +20535,7 @@
         <v>46279</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20576,7 +20608,7 @@
         <v>46223</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20649,7 +20681,7 @@
         <v>46168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20722,7 +20754,7 @@
         <v>46136</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20800,7 +20832,7 @@
         <v>44883</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20878,7 +20910,7 @@
         <v>46281</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20951,7 +20983,7 @@
         <v>46210</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21029,7 +21061,7 @@
         <v>45537</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21102,7 +21134,7 @@
         <v>45573</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21175,7 +21207,7 @@
         <v>45597</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21248,7 +21280,7 @@
         <v>44531</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21326,7 +21358,7 @@
         <v>45817</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21399,7 +21431,7 @@
         <v>45638</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21472,7 +21504,7 @@
         <v>45094</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21545,7 +21577,7 @@
         <v>45721</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21618,7 +21650,7 @@
         <v>45824</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21691,7 +21723,7 @@
         <v>45835</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21764,7 +21796,7 @@
         <v>45785</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21837,7 +21869,7 @@
         <v>45799</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21910,7 +21942,7 @@
         <v>45209</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21983,7 +22015,7 @@
         <v>44858</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22056,7 +22088,7 @@
         <v>44936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22129,7 +22161,7 @@
         <v>45348</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22202,7 +22234,7 @@
         <v>45434</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22280,7 +22312,7 @@
         <v>45434</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22358,7 +22390,7 @@
         <v>45558</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22436,7 +22468,7 @@
         <v>45558</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22514,7 +22546,7 @@
         <v>44599</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22587,7 +22619,7 @@
         <v>44701</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22660,7 +22692,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22738,7 +22770,7 @@
         <v>44936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22811,7 +22843,7 @@
         <v>44805</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22884,7 +22916,7 @@
         <v>45558</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22962,7 +22994,7 @@
         <v>44701</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23035,7 +23067,7 @@
         <v>45109</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23108,7 +23140,7 @@
         <v>44853</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23181,7 +23213,7 @@
         <v>44859</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23254,7 +23286,7 @@
         <v>45579</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23327,7 +23359,7 @@
         <v>45558</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23405,7 +23437,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23478,7 +23510,7 @@
         <v>45947</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23551,7 +23583,7 @@
         <v>46034</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23624,7 +23656,7 @@
         <v>46044</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23702,7 +23734,7 @@
         <v>46210</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23780,7 +23812,7 @@
         <v>46210</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23858,7 +23890,7 @@
         <v>46210</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE294"/>
+  <dimension ref="A1:AE296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45391</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>46199</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45544</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45903</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>46057</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54644-2023</t>
+          <t>A 31525-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45235</v>
+        <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -2446,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2473,156 +2473,156 @@
         <v>3</v>
       </c>
       <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Kruskantarell
+Stjärtmes</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 31525-2026 artfynd.xlsx", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 31525-2026 karta.png", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 31525-2026 georefererad karta.tif", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 31525-2026 FSC-klagomål.docx", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 31525-2026 FSC-klagomål mail.docx", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 31525-2026 tillsynsbegäran.docx", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 31525-2026 tillsynsbegäran mail.docx", "A 31525-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 31525-2026 prioriterade fågelarter.docx", "A 31525-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 54644-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45235</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Havstulpanlav
 Spillkråka
 Skogsduva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 54644-2023 artfynd.xlsx", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 54644-2023 karta.png", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 54644-2023 georefererad karta.tif", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 54644-2023 FSC-klagomål.docx", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 54644-2023 FSC-klagomål mail.docx", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 54644-2023 tillsynsbegäran.docx", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 54644-2023 tillsynsbegäran mail.docx", "A 54644-2023")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 54644-2023 prioriterade fågelarter.docx", "A 54644-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 31525-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Kruskantarell
-Stjärtmes</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 31525-2026 artfynd.xlsx", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 31525-2026 karta.png", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 31525-2026 georefererad karta.tif", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 31525-2026 FSC-klagomål.docx", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 31525-2026 FSC-klagomål mail.docx", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 31525-2026 tillsynsbegäran.docx", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 31525-2026 tillsynsbegäran mail.docx", "A 31525-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 31525-2026 prioriterade fågelarter.docx", "A 31525-2026")</f>
         <v/>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
         <v>44858</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>44596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>44633</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20702-2023</t>
+          <t>A 59769-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3288,14 +3288,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45058</v>
+        <v>45992</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,11 +3307,16 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3341,158 +3346,153 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 59769-2025 artfynd.xlsx", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 59769-2025 karta.png", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 59769-2025 georefererad karta.tif", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 59769-2025 FSC-klagomål.docx", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 59769-2025 FSC-klagomål mail.docx", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 59769-2025 tillsynsbegäran.docx", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 59769-2025 tillsynsbegäran mail.docx", "A 59769-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 59769-2025 prioriterade fågelarter.docx", "A 59769-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 20702-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45058</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Svinrot
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 20702-2023 artfynd.xlsx", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 20702-2023 karta.png", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 20702-2023 georefererad karta.tif", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 20702-2023 FSC-klagomål.docx", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 20702-2023 FSC-klagomål mail.docx", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 20702-2023 tillsynsbegäran.docx", "A 20702-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 20702-2023 tillsynsbegäran mail.docx", "A 20702-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 59769-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 59769-2025 artfynd.xlsx", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 59769-2025 karta.png", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 59769-2025 georefererad karta.tif", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 59769-2025 FSC-klagomål.docx", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 59769-2025 FSC-klagomål mail.docx", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 59769-2025 tillsynsbegäran.docx", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 59769-2025 tillsynsbegäran mail.docx", "A 59769-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 59769-2025 prioriterade fågelarter.docx", "A 59769-2025")</f>
         <v/>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
         <v>46202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45006</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44754</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46030</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45015</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61049-2025</t>
+          <t>A 61058-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4058,7 +4058,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4116,46 +4116,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 61049-2025 artfynd.xlsx", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 61058-2025 artfynd.xlsx", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 61049-2025 karta.png", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 61058-2025 karta.png", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 61049-2025 georefererad karta.tif", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 61058-2025 georefererad karta.tif", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 61049-2025 FSC-klagomål.docx", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 61058-2025 FSC-klagomål.docx", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 61049-2025 FSC-klagomål mail.docx", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 61058-2025 FSC-klagomål mail.docx", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 61049-2025 tillsynsbegäran.docx", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 61058-2025 tillsynsbegäran.docx", "A 61058-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 61049-2025 tillsynsbegäran mail.docx", "A 61049-2025")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 61049-2025 prioriterade fågelarter.docx", "A 61049-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 61058-2025 tillsynsbegäran mail.docx", "A 61058-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21788-2026</t>
+          <t>A 61049-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4169,10 +4165,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46150</v>
+        <v>46000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4184,17 +4180,22 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4209,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4225,42 +4226,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 21788-2026 artfynd.xlsx", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 61049-2025 artfynd.xlsx", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 21788-2026 karta.png", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 61049-2025 karta.png", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 21788-2026 georefererad karta.tif", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 61049-2025 georefererad karta.tif", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 21788-2026 FSC-klagomål.docx", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 61049-2025 FSC-klagomål.docx", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 21788-2026 FSC-klagomål mail.docx", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 61049-2025 FSC-klagomål mail.docx", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 21788-2026 tillsynsbegäran.docx", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 61049-2025 tillsynsbegäran.docx", "A 61049-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 21788-2026 tillsynsbegäran mail.docx", "A 21788-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 61049-2025 tillsynsbegäran mail.docx", "A 61049-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 61049-2025 prioriterade fågelarter.docx", "A 61049-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15810-2024</t>
+          <t>A 21788-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45404</v>
+        <v>46150</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4289,13 +4294,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4319,10 +4319,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4335,42 +4335,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 15810-2024 artfynd.xlsx", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 21788-2026 artfynd.xlsx", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 15810-2024 karta.png", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 21788-2026 karta.png", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 15810-2024 georefererad karta.tif", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 21788-2026 georefererad karta.tif", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 15810-2024 FSC-klagomål.docx", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 21788-2026 FSC-klagomål.docx", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 15810-2024 FSC-klagomål mail.docx", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 21788-2026 FSC-klagomål mail.docx", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 15810-2024 tillsynsbegäran.docx", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 21788-2026 tillsynsbegäran.docx", "A 21788-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 15810-2024 tillsynsbegäran mail.docx", "A 15810-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 21788-2026 tillsynsbegäran mail.docx", "A 21788-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44885-2022</t>
+          <t>A 15810-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44841</v>
+        <v>45404</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,21 +4399,26 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -4424,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4436,39 +4441,39 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 44885-2022 artfynd.xlsx", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 15810-2024 artfynd.xlsx", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 44885-2022 karta.png", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 15810-2024 karta.png", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 44885-2022 georefererad karta.tif", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 15810-2024 georefererad karta.tif", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 44885-2022 FSC-klagomål.docx", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 15810-2024 FSC-klagomål.docx", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 44885-2022 FSC-klagomål mail.docx", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 15810-2024 FSC-klagomål mail.docx", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 44885-2022 tillsynsbegäran.docx", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 15810-2024 tillsynsbegäran.docx", "A 15810-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 44885-2022 tillsynsbegäran mail.docx", "A 44885-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 15810-2024 tillsynsbegäran mail.docx", "A 15810-2024")</f>
         <v/>
       </c>
     </row>
@@ -4492,7 +4497,7 @@
         <v>46055</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4580,7 +4585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46147-2022</t>
+          <t>A 44885-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44846</v>
+        <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4646,46 +4651,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 46147-2022 artfynd.xlsx", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 44885-2022 artfynd.xlsx", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 46147-2022 karta.png", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 44885-2022 karta.png", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 46147-2022 georefererad karta.tif", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 44885-2022 georefererad karta.tif", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 46147-2022 FSC-klagomål.docx", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 44885-2022 FSC-klagomål.docx", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 46147-2022 FSC-klagomål mail.docx", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 44885-2022 FSC-klagomål mail.docx", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 46147-2022 tillsynsbegäran.docx", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 44885-2022 tillsynsbegäran.docx", "A 44885-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 46147-2022 tillsynsbegäran mail.docx", "A 46147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 44885-2022 tillsynsbegäran mail.docx", "A 44885-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61058-2025</t>
+          <t>A 46147-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4699,10 +4704,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46000</v>
+        <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4714,19 +4719,14 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4760,42 +4760,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 61058-2025 artfynd.xlsx", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 46147-2022 artfynd.xlsx", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 61058-2025 karta.png", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 46147-2022 karta.png", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 61058-2025 georefererad karta.tif", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 46147-2022 georefererad karta.tif", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 61058-2025 FSC-klagomål.docx", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 46147-2022 FSC-klagomål.docx", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 61058-2025 FSC-klagomål mail.docx", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 46147-2022 FSC-klagomål mail.docx", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 61058-2025 tillsynsbegäran.docx", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 46147-2022 tillsynsbegäran.docx", "A 46147-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 61058-2025 tillsynsbegäran mail.docx", "A 61058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 46147-2022 tillsynsbegäran mail.docx", "A 46147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10000-2025</t>
+          <t>A 31279-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45719</v>
+        <v>46218</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4869,38 +4869,38 @@
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 10000-2025 artfynd.xlsx", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 31279-2026 artfynd.xlsx", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 10000-2025 karta.png", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 31279-2026 karta.png", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 10000-2025 georefererad karta.tif", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 31279-2026 georefererad karta.tif", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 10000-2025 FSC-klagomål.docx", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 31279-2026 FSC-klagomål.docx", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 10000-2025 FSC-klagomål mail.docx", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 31279-2026 FSC-klagomål mail.docx", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 10000-2025 tillsynsbegäran.docx", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 31279-2026 tillsynsbegäran.docx", "A 31279-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 10000-2025 tillsynsbegäran mail.docx", "A 10000-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 31279-2026 tillsynsbegäran mail.docx", "A 31279-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31279-2026</t>
+          <t>A 37224-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46218</v>
+        <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,13 +4930,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4963,49 +4963,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 31279-2026 artfynd.xlsx", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37224-2026 artfynd.xlsx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 31279-2026 karta.png", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37224-2026 karta.png", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 31279-2026 georefererad karta.tif", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37224-2026 georefererad karta.tif", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 31279-2026 FSC-klagomål.docx", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37224-2026 FSC-klagomål.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 31279-2026 FSC-klagomål mail.docx", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37224-2026 FSC-klagomål mail.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 31279-2026 tillsynsbegäran.docx", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37224-2026 tillsynsbegäran.docx", "A 37224-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 31279-2026 tillsynsbegäran mail.docx", "A 31279-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37224-2026 tillsynsbegäran mail.docx", "A 37224-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51276-2024</t>
+          <t>A 10000-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45603</v>
+        <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,16 +5035,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5071,46 +5071,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 51276-2024 artfynd.xlsx", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 10000-2025 artfynd.xlsx", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 51276-2024 karta.png", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 10000-2025 karta.png", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 51276-2024 georefererad karta.tif", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 10000-2025 georefererad karta.tif", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 51276-2024 FSC-klagomål.docx", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 10000-2025 FSC-klagomål.docx", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 51276-2024 FSC-klagomål mail.docx", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 10000-2025 FSC-klagomål mail.docx", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 51276-2024 tillsynsbegäran.docx", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 10000-2025 tillsynsbegäran.docx", "A 10000-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 51276-2024 tillsynsbegäran mail.docx", "A 51276-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 10000-2025 tillsynsbegäran mail.docx", "A 10000-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37224-2026</t>
+          <t>A 51276-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46274</v>
+        <v>45603</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,17 +5140,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5173,42 +5173,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37224-2026 artfynd.xlsx", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 51276-2024 artfynd.xlsx", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37224-2026 karta.png", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 51276-2024 karta.png", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37224-2026 georefererad karta.tif", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 51276-2024 georefererad karta.tif", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37224-2026 FSC-klagomål.docx", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 51276-2024 FSC-klagomål.docx", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37224-2026 FSC-klagomål mail.docx", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 51276-2024 FSC-klagomål mail.docx", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37224-2026 tillsynsbegäran.docx", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 51276-2024 tillsynsbegäran.docx", "A 51276-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37224-2026 tillsynsbegäran mail.docx", "A 37224-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 51276-2024 tillsynsbegäran mail.docx", "A 51276-2024")</f>
         <v/>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
         <v>44992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45217</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44859</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44665</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44489</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19097-2022</t>
+          <t>A 20010-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44691</v>
+        <v>44697</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6015,7 +6015,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20010-2022</t>
+          <t>A 19999-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6032,7 +6032,7 @@
         <v>44697</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6088,7 +6088,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19999-2022</t>
+          <t>A 69392-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44697</v>
+        <v>44531</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 69392-2021</t>
+          <t>A 19097-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44531</v>
+        <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6251,7 +6251,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53582-2022</t>
+          <t>A 10055-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44875</v>
+        <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6419,13 +6419,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10055-2022</t>
+          <t>A 53582-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44621</v>
+        <v>44875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6497,8 +6492,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>44608</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44575</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44782</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44880</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44700</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45660</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3198-2023</t>
+          <t>A 34051-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44944</v>
+        <v>45523</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25393-2023</t>
+          <t>A 3198-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45079</v>
+        <v>44944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
         <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34051-2024</t>
+          <t>A 25393-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45523</v>
+        <v>45079</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28844-2023</t>
+          <t>A 37967-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45104</v>
+        <v>45544</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37967-2024</t>
+          <t>A 28844-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45544</v>
+        <v>45104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>45328</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44930</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45519</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 217-2023</t>
+          <t>A 15070-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44928</v>
+        <v>45399</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7987,8 +7987,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8031,7 +8036,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15070-2024</t>
+          <t>A 217-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8045,10 +8050,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45399</v>
+        <v>44928</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8060,13 +8065,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>45163</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5256-2022</t>
+          <t>A 58642-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44593</v>
+        <v>44489</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8255,7 +8255,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58642-2021</t>
+          <t>A 25069-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8269,10 +8269,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44489</v>
+        <v>45086</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25069-2023</t>
+          <t>A 5256-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45086</v>
+        <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8418,7 +8418,7 @@
         <v>45040</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45077</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45103</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44891-2022</t>
+          <t>A 17856-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44841</v>
+        <v>45419</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8795,8 +8795,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8839,7 +8844,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17856-2024</t>
+          <t>A 44891-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8853,10 +8858,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45419</v>
+        <v>44841</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8868,13 +8873,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
         <v>45739</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44991</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45581</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37068-2023</t>
+          <t>A 39244-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45155</v>
+        <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9287,7 +9287,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39244-2022</t>
+          <t>A 20717-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44817</v>
+        <v>45055</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9360,7 +9360,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20717-2023</t>
+          <t>A 37068-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45055</v>
+        <v>45155</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 55588-2021</t>
+          <t>A 24813-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44475</v>
+        <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9506,7 +9506,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52286-2023</t>
+          <t>A 52851-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45224</v>
+        <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9579,7 +9579,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46619-2024</t>
+          <t>A 55588-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45583</v>
+        <v>44475</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24333-2022</t>
+          <t>A 52286-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44726</v>
+        <v>45224</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9725,7 +9725,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 56089-2021</t>
+          <t>A 46619-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44477</v>
+        <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>20.9</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9798,7 +9798,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52851-2024</t>
+          <t>A 43855-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9812,10 +9812,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45610</v>
+        <v>44838</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9827,8 +9827,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9871,7 +9876,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54348-2022</t>
+          <t>A 24333-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9885,10 +9890,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44882</v>
+        <v>44726</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9901,7 +9906,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9944,7 +9949,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38156-2022</t>
+          <t>A 56089-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44812</v>
+        <v>44477</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9974,7 +9979,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10017,7 +10022,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40710-2023</t>
+          <t>A 42627-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10031,10 +10036,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45170</v>
+        <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10047,7 +10052,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10107,7 +10112,7 @@
         <v>46000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10168,7 +10173,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43855-2022</t>
+          <t>A 20088-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10182,10 +10187,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44838</v>
+        <v>46136</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10203,7 +10208,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10246,7 +10251,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20088-2026</t>
+          <t>A 34479-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10260,10 +10265,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46136</v>
+        <v>45847</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10275,13 +10280,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10324,7 +10324,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55833-2023</t>
+          <t>A 45096-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10334,14 +10334,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45239</v>
+        <v>45919</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10397,7 +10397,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20128-2023</t>
+          <t>A 54348-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45055</v>
+        <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10470,7 +10470,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2252-2025</t>
+          <t>A 38156-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45673</v>
+        <v>44812</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10543,7 +10543,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42627-2025</t>
+          <t>A 40710-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45905</v>
+        <v>45170</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10616,7 +10616,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61682-2023</t>
+          <t>A 55833-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10626,14 +10626,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45264</v>
+        <v>45239</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10689,7 +10689,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11676-2023</t>
+          <t>A 20627-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44992</v>
+        <v>46141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10718,13 +10718,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10767,7 +10762,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51844-2023</t>
+          <t>A 20629-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10781,10 +10776,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45223</v>
+        <v>46141</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10797,7 +10792,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10840,7 +10835,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 34479-2025</t>
+          <t>A 20128-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10854,10 +10849,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45847</v>
+        <v>45055</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10870,7 +10865,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10913,7 +10908,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20627-2026</t>
+          <t>A 2252-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10927,10 +10922,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46141</v>
+        <v>45673</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10943,7 +10938,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10986,7 +10981,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20629-2026</t>
+          <t>A 21602-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11000,10 +10995,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11016,7 +11011,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11059,7 +11054,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28847-2023</t>
+          <t>A 21609-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11073,10 +11068,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45104</v>
+        <v>46149</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11132,7 +11127,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15442-2022</t>
+          <t>A 21608-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11146,10 +11141,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44659</v>
+        <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11162,7 +11157,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11205,7 +11200,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2755-2023</t>
+          <t>A 21599-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11219,10 +11214,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44944</v>
+        <v>46149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11234,13 +11229,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11283,7 +11273,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 49370-2023</t>
+          <t>A 21607-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11297,10 +11287,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45211</v>
+        <v>46149</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11313,7 +11303,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11356,7 +11346,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 45096-2025</t>
+          <t>A 21778-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11370,10 +11360,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45919</v>
+        <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11386,7 +11376,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11429,7 +11419,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46728-2023</t>
+          <t>A 61682-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11439,14 +11429,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45198</v>
+        <v>45264</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11459,7 +11449,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11502,7 +11492,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3498-2024</t>
+          <t>A 63499-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11516,10 +11506,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45320</v>
+        <v>46013</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11532,7 +11522,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11575,7 +11565,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 41294-2022</t>
+          <t>A 11676-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11589,10 +11579,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44825</v>
+        <v>44992</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11604,8 +11594,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11648,7 +11643,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39097-2024</t>
+          <t>A 51844-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11662,10 +11657,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45548</v>
+        <v>45223</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11678,7 +11673,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11721,7 +11716,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 8712-2023</t>
+          <t>A 28847-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11735,10 +11730,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44978</v>
+        <v>45104</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11751,7 +11746,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11794,7 +11789,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 49073-2024</t>
+          <t>A 40092-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11808,10 +11803,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45594</v>
+        <v>45894</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11824,7 +11819,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11867,7 +11862,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21602-2026</t>
+          <t>A 15442-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11881,10 +11876,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46149</v>
+        <v>44659</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11897,7 +11892,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11940,7 +11935,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21609-2026</t>
+          <t>A 2755-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11954,10 +11949,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46149</v>
+        <v>44944</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11969,8 +11964,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12013,7 +12013,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 40092-2025</t>
+          <t>A 49370-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45894</v>
+        <v>45211</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12086,7 +12086,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7661-2025</t>
+          <t>A 51396-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45706</v>
+        <v>45950</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12159,7 +12159,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21608-2026</t>
+          <t>A 46728-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12169,14 +12169,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46149</v>
+        <v>45198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21599-2026</t>
+          <t>A 23220-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12246,10 +12246,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46149</v>
+        <v>46162</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12305,7 +12305,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21607-2026</t>
+          <t>A 55696-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12319,10 +12319,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46149</v>
+        <v>45972</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12378,7 +12378,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3183-2023</t>
+          <t>A 33462-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12392,10 +12392,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44944</v>
+        <v>45841</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12451,7 +12451,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 51396-2025</t>
+          <t>A 3498-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12465,10 +12465,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45950</v>
+        <v>45320</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12524,7 +12524,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 48965-2023</t>
+          <t>A 41294-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12538,10 +12538,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45209</v>
+        <v>44825</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12597,7 +12597,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9270-2022</t>
+          <t>A 39097-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12611,10 +12611,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44616</v>
+        <v>45548</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36842-2024</t>
+          <t>A 8712-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45538</v>
+        <v>44978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12699,13 +12699,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12748,7 +12743,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 21778-2026</t>
+          <t>A 49073-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12762,10 +12757,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46150</v>
+        <v>45594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12778,7 +12773,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12821,7 +12816,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4321-2024</t>
+          <t>A 57687-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12835,10 +12830,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45324</v>
+        <v>45981</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12850,8 +12845,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12894,7 +12894,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8500-2023</t>
+          <t>A 7661-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44977</v>
+        <v>45706</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 63499-2025</t>
+          <t>A 3183-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46013</v>
+        <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13040,7 +13040,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 55291-2023</t>
+          <t>A 48965-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45237</v>
+        <v>45209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13113,7 +13113,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 55696-2025</t>
+          <t>A 9270-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45972</v>
+        <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13186,7 +13186,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33462-2025</t>
+          <t>A 36842-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45841</v>
+        <v>45538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13215,8 +13215,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13259,7 +13264,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 69041-2021</t>
+          <t>A 42006-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13269,14 +13274,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44529</v>
+        <v>45903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13289,7 +13294,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13332,7 +13337,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 57687-2025</t>
+          <t>A 4321-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13346,10 +13351,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45981</v>
+        <v>45324</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13361,13 +13366,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13410,7 +13410,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23260-2023</t>
+          <t>A 8500-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13424,10 +13424,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45075</v>
+        <v>44977</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13483,7 +13483,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 55586-2021</t>
+          <t>A 55291-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13497,10 +13497,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44475</v>
+        <v>45237</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13556,7 +13556,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23220-2026</t>
+          <t>A 25423-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13570,10 +13570,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13629,7 +13629,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10695-2023</t>
+          <t>A 25424-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13643,10 +13643,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44988</v>
+        <v>46177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 42006-2025</t>
+          <t>A 25721-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13716,10 +13716,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45903</v>
+        <v>46178</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13775,7 +13775,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14614-2023</t>
+          <t>A 69041-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45013</v>
+        <v>44529</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13848,7 +13848,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8017-2022</t>
+          <t>A 6447-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13862,10 +13862,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44609</v>
+        <v>46055</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>45946</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>46027</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13995-2025</t>
+          <t>A 2806-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14081,10 +14081,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45739</v>
+        <v>46038</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 42275-2024</t>
+          <t>A 23260-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45562</v>
+        <v>45075</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14169,13 +14169,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14218,7 +14213,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24034-2023</t>
+          <t>A 55586-2021</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14232,10 +14227,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45078</v>
+        <v>44475</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14248,7 +14243,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14291,7 +14286,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5196-2022</t>
+          <t>A 4968-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14305,10 +14300,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44593</v>
+        <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14321,7 +14316,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14364,7 +14359,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 2806-2026</t>
+          <t>A 10695-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14378,10 +14373,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46038</v>
+        <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14394,7 +14389,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14437,7 +14432,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45641-2022</t>
+          <t>A 14614-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14447,14 +14442,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44845</v>
+        <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14467,7 +14462,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14510,7 +14505,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21636-2024</t>
+          <t>A 53289-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14524,10 +14519,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45442</v>
+        <v>45958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14540,7 +14535,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14583,7 +14578,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 4968-2026</t>
+          <t>A 53290-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14597,10 +14592,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46049</v>
+        <v>45958</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14613,7 +14608,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14656,7 +14651,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25423-2026</t>
+          <t>A 9488-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14670,10 +14665,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46177</v>
+        <v>46071</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14686,7 +14681,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14729,7 +14724,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25424-2026</t>
+          <t>A 29338-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14743,10 +14738,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46177</v>
+        <v>46202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14759,7 +14754,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14802,7 +14797,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 60783-2023</t>
+          <t>A 8017-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14816,10 +14811,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45260</v>
+        <v>44609</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14832,7 +14827,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14875,7 +14870,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14619-2023</t>
+          <t>A 13995-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14889,10 +14884,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45013</v>
+        <v>45739</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14905,7 +14900,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14948,7 +14943,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25721-2026</t>
+          <t>A 42275-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14962,10 +14957,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46178</v>
+        <v>45562</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14977,8 +14972,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15021,7 +15021,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27454-2024</t>
+          <t>A 33181-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45474</v>
+        <v>46245</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11335-2023</t>
+          <t>A 24034-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15108,10 +15108,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44993</v>
+        <v>45078</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15167,7 +15167,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6447-2026</t>
+          <t>A 5196-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15181,10 +15181,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46055</v>
+        <v>44593</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15240,7 +15240,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13363-2023</t>
+          <t>A 14774-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45005</v>
+        <v>46101</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15269,13 +15269,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15318,7 +15313,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5151-2022</t>
+          <t>A 45641-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15328,14 +15323,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44593</v>
+        <v>44845</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15348,7 +15343,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15391,7 +15386,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53289-2025</t>
+          <t>A 21636-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15405,10 +15400,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45958</v>
+        <v>45442</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15421,7 +15416,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15464,7 +15459,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 53290-2025</t>
+          <t>A 60783-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15478,10 +15473,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45958</v>
+        <v>45260</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15494,7 +15489,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15537,7 +15532,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 23741-2023</t>
+          <t>A 14619-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15551,10 +15546,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45077</v>
+        <v>45013</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15567,7 +15562,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15610,7 +15605,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 9488-2026</t>
+          <t>A 27454-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15624,10 +15619,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46071</v>
+        <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15640,7 +15635,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15683,7 +15678,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 47870-2022</t>
+          <t>A 30240-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15697,10 +15692,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44855</v>
+        <v>46206</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,8 +15707,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>10.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15756,7 +15756,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27813-2023</t>
+          <t>A 11335-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15770,10 +15770,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45098</v>
+        <v>44993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58387-2022</t>
+          <t>A 13363-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44901</v>
+        <v>45005</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15860,11 +15860,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15907,7 +15907,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27452-2024</t>
+          <t>A 5151-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15921,10 +15921,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45474</v>
+        <v>44593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15980,7 +15980,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 45596-2024</t>
+          <t>A 23741-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45579</v>
+        <v>45077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38323-2023</t>
+          <t>A 33783-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16067,10 +16067,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45161</v>
+        <v>46251</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38325-2023</t>
+          <t>A 30215-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16140,10 +16140,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45161</v>
+        <v>46206</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16155,8 +16155,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16199,7 +16204,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21654-2024</t>
+          <t>A 30422-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16213,10 +16218,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45442</v>
+        <v>46209</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16228,8 +16233,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16272,7 +16282,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 14774-2026</t>
+          <t>A 47870-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16286,10 +16296,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46101</v>
+        <v>44855</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16302,7 +16312,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16345,7 +16355,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 1280-2023</t>
+          <t>A 34199-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16359,10 +16369,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44936</v>
+        <v>46253</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16375,7 +16385,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16418,7 +16428,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 20591-2023</t>
+          <t>A 30353-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16432,10 +16442,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45055</v>
+        <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16447,8 +16457,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16491,7 +16506,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52877-2022</t>
+          <t>A 30346-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16505,10 +16520,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44875</v>
+        <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16520,8 +16535,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16564,7 +16584,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29338-2026</t>
+          <t>A 27813-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16578,10 +16598,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46202</v>
+        <v>45098</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16594,7 +16614,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16637,7 +16657,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 11705-2023</t>
+          <t>A 58387-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16651,10 +16671,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44992</v>
+        <v>44901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16666,8 +16686,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16710,7 +16735,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 64224-2023</t>
+          <t>A 27452-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16724,10 +16749,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45279</v>
+        <v>45474</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16740,7 +16765,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16783,7 +16808,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20002-2022</t>
+          <t>A 30356-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16797,10 +16822,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44697</v>
+        <v>46209</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16812,8 +16837,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16856,7 +16886,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 47856-2024</t>
+          <t>A 45596-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16870,10 +16900,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45588</v>
+        <v>45579</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16886,7 +16916,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16929,7 +16959,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 49686-2023</t>
+          <t>A 38323-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16943,10 +16973,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45212</v>
+        <v>45161</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16959,7 +16989,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17002,7 +17032,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 68856-2021</t>
+          <t>A 38325-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17016,10 +17046,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44530</v>
+        <v>45161</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17032,7 +17062,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17075,7 +17105,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 46835-2023</t>
+          <t>A 31120-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17089,10 +17119,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45199</v>
+        <v>46216</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17105,7 +17135,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17148,7 +17178,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 5557-2022</t>
+          <t>A 21654-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17162,10 +17192,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44593</v>
+        <v>45442</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17178,7 +17208,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17221,7 +17251,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33181-2026</t>
+          <t>A 23341-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17235,10 +17265,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46245</v>
+        <v>46162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17251,7 +17281,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17294,7 +17324,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 46253-2024</t>
+          <t>A 31119-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17308,10 +17338,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45581</v>
+        <v>46216</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17323,13 +17353,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17372,7 +17397,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 39530-2023</t>
+          <t>A 31121-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17386,10 +17411,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45167</v>
+        <v>46216</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17402,7 +17427,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17445,7 +17470,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22976-2023</t>
+          <t>A 29500-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17459,10 +17484,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45072</v>
+        <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17474,8 +17499,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17518,7 +17548,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 23978-2022</t>
+          <t>A 1280-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17532,10 +17562,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44722</v>
+        <v>44936</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17548,7 +17578,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>9.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17591,7 +17621,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 15812-2024</t>
+          <t>A 20591-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17605,10 +17635,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45404</v>
+        <v>45055</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17620,13 +17650,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17669,7 +17694,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38945-2023</t>
+          <t>A 52877-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17683,10 +17708,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45163</v>
+        <v>44875</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17699,7 +17724,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17742,7 +17767,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 55587-2021</t>
+          <t>A 11705-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17756,10 +17781,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44475</v>
+        <v>44992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17772,7 +17797,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17815,7 +17840,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 30240-2026</t>
+          <t>A 64224-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17829,10 +17854,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46206</v>
+        <v>45279</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17844,13 +17869,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17893,7 +17913,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 23874-2022</t>
+          <t>A 35635-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17907,10 +17927,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44722</v>
+        <v>46265</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17923,7 +17943,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17966,7 +17986,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33783-2026</t>
+          <t>A 20002-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17980,10 +18000,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46251</v>
+        <v>44697</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17996,7 +18016,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18039,7 +18059,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30215-2026</t>
+          <t>A 47856-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18053,10 +18073,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46206</v>
+        <v>45588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18068,13 +18088,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18117,7 +18132,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 9142-2025</t>
+          <t>A 49686-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18131,10 +18146,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45714</v>
+        <v>45212</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18147,7 +18162,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18190,7 +18205,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 30422-2026</t>
+          <t>A 68856-2021</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18204,10 +18219,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46209</v>
+        <v>44530</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18219,13 +18234,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18268,7 +18278,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28247-2023</t>
+          <t>A 46835-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18282,10 +18292,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45099</v>
+        <v>45199</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18298,7 +18308,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18341,7 +18351,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 56759-2023</t>
+          <t>A 5557-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18355,10 +18365,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45238</v>
+        <v>44593</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18371,7 +18381,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18414,7 +18424,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 4301-2024</t>
+          <t>A 36480-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18428,10 +18438,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45324</v>
+        <v>46269</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18443,13 +18453,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18492,7 +18497,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 34199-2026</t>
+          <t>A 36475-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18506,10 +18511,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46253</v>
+        <v>46269</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18522,7 +18527,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18565,7 +18570,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 30353-2026</t>
+          <t>A 30520-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18579,10 +18584,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18596,11 +18601,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18643,7 +18648,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 30346-2026</t>
+          <t>A 46253-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18657,10 +18662,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46209</v>
+        <v>45581</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18678,7 +18683,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>5.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18721,7 +18726,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22202-2023</t>
+          <t>A 39530-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18735,10 +18740,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45069</v>
+        <v>45167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18751,7 +18756,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18794,7 +18799,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 30356-2026</t>
+          <t>A 22976-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18808,10 +18813,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46209</v>
+        <v>45072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18823,13 +18828,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18872,7 +18872,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 20012-2022</t>
+          <t>A 23978-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18886,10 +18886,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44697</v>
+        <v>44722</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>17.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18945,7 +18945,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 16418-2025</t>
+          <t>A 15812-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18959,10 +18959,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45751</v>
+        <v>45404</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18974,8 +18974,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19018,7 +19023,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31120-2026</t>
+          <t>A 38945-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19032,10 +19037,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46216</v>
+        <v>45163</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19048,7 +19053,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19091,7 +19096,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23341-2026</t>
+          <t>A 55587-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19105,10 +19110,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46162</v>
+        <v>44475</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19121,7 +19126,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19164,7 +19169,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 63720-2023</t>
+          <t>A 23874-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19178,10 +19183,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45275</v>
+        <v>44722</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19194,7 +19199,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19237,7 +19242,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 14278-2024</t>
+          <t>A 9142-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19251,10 +19256,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45393</v>
+        <v>45714</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19267,7 +19272,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19310,7 +19315,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31119-2026</t>
+          <t>A 37724-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19324,10 +19329,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46216</v>
+        <v>46279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19340,7 +19345,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19383,7 +19388,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 31121-2026</t>
+          <t>A 28247-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19397,10 +19402,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46216</v>
+        <v>45099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19413,7 +19418,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19456,7 +19461,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 47869-2022</t>
+          <t>A 31588-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19470,10 +19475,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44855</v>
+        <v>46223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19486,7 +19491,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19529,7 +19534,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 29500-2026</t>
+          <t>A 24138-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19543,10 +19548,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46198</v>
+        <v>46168</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19558,13 +19563,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19607,7 +19607,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 6615-2024</t>
+          <t>A 56759-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19621,10 +19621,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45341</v>
+        <v>45238</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.4</v>
+        <v>7.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19680,7 +19680,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24647-2023</t>
+          <t>A 4301-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19694,10 +19694,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45084</v>
+        <v>45324</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19758,7 +19758,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 13420-2023</t>
+          <t>A 22202-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19772,10 +19772,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45005</v>
+        <v>45069</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19787,13 +19787,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19836,7 +19831,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 35635-2026</t>
+          <t>A 20082-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19850,10 +19845,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46265</v>
+        <v>46136</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19865,8 +19860,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19909,7 +19909,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 42281-2024</t>
+          <t>A 20012-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19923,10 +19923,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45562</v>
+        <v>44697</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19938,13 +19938,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>0.6</v>
+        <v>17.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19987,7 +19982,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 42284-2024</t>
+          <t>A 38234-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20001,10 +19996,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45562</v>
+        <v>46281</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20016,13 +20011,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20065,7 +20055,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 3489-2024</t>
+          <t>A 30514-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20079,10 +20069,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45320</v>
+        <v>46210</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20094,8 +20084,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20138,7 +20133,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 36480-2026</t>
+          <t>A 16418-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20152,10 +20147,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46269</v>
+        <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20168,7 +20163,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20211,7 +20206,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 36475-2026</t>
+          <t>A 63720-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20225,10 +20220,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46269</v>
+        <v>45275</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20241,7 +20236,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20284,7 +20279,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 30520-2026</t>
+          <t>A 14278-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20298,10 +20293,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46210</v>
+        <v>45393</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20313,13 +20308,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20362,7 +20352,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 40173-2024</t>
+          <t>A 47869-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20376,10 +20366,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45554</v>
+        <v>44855</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20389,11 +20379,6 @@
       <c r="G247" t="inlineStr">
         <is>
           <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -20440,7 +20425,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 7746-2024</t>
+          <t>A 38880-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20454,10 +20439,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45349</v>
+        <v>46286</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20469,13 +20454,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20518,7 +20498,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 37724-2026</t>
+          <t>A 6615-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20532,10 +20512,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46279</v>
+        <v>45341</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20548,7 +20528,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20591,7 +20571,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 31588-2026</t>
+          <t>A 24647-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20605,10 +20585,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46223</v>
+        <v>45084</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20620,8 +20600,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>3.5</v>
+        <v>11.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20664,7 +20649,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 24138-2026</t>
+          <t>A 13420-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20678,10 +20663,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46168</v>
+        <v>45005</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20693,8 +20678,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20737,7 +20727,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20082-2026</t>
+          <t>A 39060-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20751,10 +20741,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46136</v>
+        <v>46287</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20766,13 +20756,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20815,7 +20800,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 55613-2022</t>
+          <t>A 42281-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20829,10 +20814,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44883</v>
+        <v>45562</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20846,11 +20831,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20893,7 +20878,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 38234-2026</t>
+          <t>A 42284-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20907,10 +20892,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46281</v>
+        <v>45562</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20922,8 +20907,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20966,7 +20956,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 30514-2026</t>
+          <t>A 3489-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20980,10 +20970,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46210</v>
+        <v>45320</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20995,13 +20985,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21044,7 +21029,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 36606-2024</t>
+          <t>A 40173-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21058,10 +21043,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45537</v>
+        <v>45554</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21073,8 +21058,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21117,7 +21107,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 44228-2024</t>
+          <t>A 7746-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21131,10 +21121,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45573</v>
+        <v>45349</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21146,8 +21136,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21190,7 +21185,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 49989-2024</t>
+          <t>A 55613-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21204,10 +21199,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45597</v>
+        <v>44883</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21219,8 +21214,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21263,7 +21263,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 69394-2021</t>
+          <t>A 36606-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21277,10 +21277,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44531</v>
+        <v>45537</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21292,13 +21292,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21341,7 +21336,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 27898-2025</t>
+          <t>A 44228-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21355,10 +21350,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45817</v>
+        <v>45573</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21371,7 +21366,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21414,7 +21409,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 59482-2024</t>
+          <t>A 49989-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21428,10 +21423,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45638</v>
+        <v>45597</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21444,7 +21439,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21487,7 +21482,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 27010-2023</t>
+          <t>A 69394-2021</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21501,10 +21496,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45094</v>
+        <v>44531</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21516,8 +21511,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21560,7 +21560,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 10544-2025</t>
+          <t>A 27898-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21574,10 +21574,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45721</v>
+        <v>45817</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21633,7 +21633,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 29284-2025</t>
+          <t>A 59482-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21643,14 +21643,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45824</v>
+        <v>45638</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21706,7 +21706,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32132-2025</t>
+          <t>A 27010-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21720,10 +21720,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45835</v>
+        <v>45094</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21779,7 +21779,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 22120-2025</t>
+          <t>A 10544-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21793,10 +21793,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45785</v>
+        <v>45721</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21852,7 +21852,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 24813-2025</t>
+          <t>A 29284-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21862,14 +21862,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45799</v>
+        <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21925,24 +21925,24 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 3541-2023</t>
+          <t>A 32132-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45209</v>
+        <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21998,24 +21998,24 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 5970-2022</t>
+          <t>A 22120-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44858</v>
+        <v>45785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>10.6</v>
+        <v>2.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22071,7 +22071,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 116-2023</t>
+          <t>S 3541-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44936</v>
+        <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>51.8</v>
+        <v>11.8</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -22144,7 +22144,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 525-2024</t>
+          <t>S 5970-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -22158,10 +22158,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45348</v>
+        <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>22.3</v>
+        <v>10.6</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -22217,7 +22217,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 1710-2024</t>
+          <t>S 116-2023</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -22231,10 +22231,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45434</v>
+        <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22246,13 +22246,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I272" t="n">
-        <v>13.4</v>
+        <v>51.8</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -22295,7 +22290,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 1713-2024</t>
+          <t>S 525-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -22309,10 +22304,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45434</v>
+        <v>45348</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22324,13 +22319,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I273" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -22373,7 +22363,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 3796-2024</t>
+          <t>S 1710-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -22383,14 +22373,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45558</v>
+        <v>45434</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22404,11 +22394,11 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.7</v>
+        <v>13.4</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -22451,7 +22441,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 3804-2024</t>
+          <t>S 1713-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -22461,14 +22451,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45558</v>
+        <v>45434</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22482,11 +22472,11 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -22529,7 +22519,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 704-2022</t>
+          <t>S 3796-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -22539,14 +22529,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>44599</v>
+        <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22558,8 +22548,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I276" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -22602,7 +22597,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 2678-2022</t>
+          <t>S 3804-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -22612,14 +22607,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44701</v>
+        <v>45558</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22631,8 +22626,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I277" t="n">
-        <v>15</v>
+        <v>1.3</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -22675,7 +22675,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 1716-2024</t>
+          <t>S 704-2022</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -22685,14 +22685,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45434</v>
+        <v>44599</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22704,13 +22704,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I278" t="n">
-        <v>29.5</v>
+        <v>0.7</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22753,7 +22748,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>S 110-2023</t>
+          <t>S 2678-2022</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22767,10 +22762,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>44936</v>
+        <v>44701</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22783,7 +22778,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>26.9</v>
+        <v>15</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22826,7 +22821,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>S 4865-2022</t>
+          <t>S 1716-2024</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22840,10 +22835,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>44805</v>
+        <v>45434</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22855,8 +22850,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I280" t="n">
-        <v>29.1</v>
+        <v>29.5</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22899,7 +22899,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>S 3792-2024</t>
+          <t>S 110-2023</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22909,14 +22909,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45558</v>
+        <v>44936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22928,13 +22928,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I281" t="n">
-        <v>0.8</v>
+        <v>26.9</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22977,7 +22972,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>S 2690-2022</t>
+          <t>S 4865-2022</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22991,10 +22986,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>44701</v>
+        <v>44805</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23007,7 +23002,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>16.3</v>
+        <v>29.1</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -23050,7 +23045,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>S 2225-2023</t>
+          <t>S 3792-2024</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -23064,10 +23059,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45109</v>
+        <v>45558</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23079,8 +23074,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I283" t="n">
-        <v>15.2</v>
+        <v>0.8</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -23123,7 +23123,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>S 5892-2022</t>
+          <t>S 2690-2022</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -23137,10 +23137,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>44853</v>
+        <v>44701</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>24.6</v>
+        <v>16.3</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -23196,7 +23196,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>S 5986-2022</t>
+          <t>S 2225-2023</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -23206,14 +23206,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>44859</v>
+        <v>45109</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>19.6</v>
+        <v>15.2</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>S 4186-2024</t>
+          <t>S 5892-2022</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -23283,10 +23283,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45579</v>
+        <v>44853</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>6.2</v>
+        <v>24.6</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -23342,7 +23342,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>S 3806-2024</t>
+          <t>S 5986-2022</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -23352,14 +23352,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45558</v>
+        <v>44859</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23371,13 +23371,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I287" t="n">
-        <v>0.1</v>
+        <v>19.6</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -23420,7 +23415,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>S 1606-2025</t>
+          <t>S 4186-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -23434,10 +23429,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45798</v>
+        <v>45579</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23450,7 +23445,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>11.7</v>
+        <v>6.2</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -23493,7 +23488,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S 2907-2025</t>
+          <t>S 3806-2024</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -23503,14 +23498,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45947</v>
+        <v>45558</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23522,8 +23517,13 @@
           <t>KLIPPAN</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I289" t="n">
-        <v>48.2</v>
+        <v>0.1</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -23566,7 +23566,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S 83-2026</t>
+          <t>S 1606-2025</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -23580,10 +23580,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>46034</v>
+        <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>8.9</v>
+        <v>11.7</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -23639,7 +23639,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>S 166-2026</t>
+          <t>S 2907-2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -23653,10 +23653,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>46044</v>
+        <v>45947</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23668,13 +23668,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I291" t="n">
-        <v>4.2</v>
+        <v>48.2</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -23717,7 +23712,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>S 2022-2026</t>
+          <t>S 83-2026</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -23731,10 +23726,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>46210</v>
+        <v>46034</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23746,13 +23741,8 @@
           <t>KLIPPAN</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>8.9</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23795,7 +23785,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>S 2019-2026</t>
+          <t>S 166-2026</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23809,10 +23799,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>46210</v>
+        <v>46044</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23830,7 +23820,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23870,10 +23860,10 @@
       </c>
       <c r="V293" s="2" t="inlineStr"/>
     </row>
-    <row r="294">
+    <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>S 2020-2026</t>
+          <t>S 2022-2026</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23890,7 +23880,7 @@
         <v>46210</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23908,45 +23898,201 @@
         </is>
       </c>
       <c r="I294" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>0</v>
+      </c>
+      <c r="V294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295" ht="15" customHeight="1">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>S 2019-2026</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E295" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>20</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>0</v>
+      </c>
+      <c r="T295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="n">
+        <v>0</v>
+      </c>
+      <c r="V295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>S 2020-2026</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E296" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
         <v>30.3</v>
       </c>
-      <c r="J294" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" t="n">
-        <v>0</v>
-      </c>
-      <c r="L294" t="n">
-        <v>0</v>
-      </c>
-      <c r="M294" t="n">
-        <v>0</v>
-      </c>
-      <c r="N294" t="n">
-        <v>0</v>
-      </c>
-      <c r="O294" t="n">
-        <v>0</v>
-      </c>
-      <c r="P294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
-      <c r="R294" t="n">
-        <v>0</v>
-      </c>
-      <c r="S294" t="n">
-        <v>0</v>
-      </c>
-      <c r="T294" t="n">
-        <v>0</v>
-      </c>
-      <c r="U294" t="n">
-        <v>0</v>
-      </c>
-      <c r="V294" s="2" t="inlineStr"/>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="n">
+        <v>0</v>
+      </c>
+      <c r="V296" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45391</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>46199</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45544</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45903</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45208</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>45235</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44880</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45581</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44858</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>44596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45992</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>45917</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44633</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45058</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>46202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46288</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>46289</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45335</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45006</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>46030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44841</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45404</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45015</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>46000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46150</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>46218</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45719</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44665</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45217</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44859</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44697</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44697</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44608</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44782</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44880</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45341</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45324</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45714</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45239</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44812</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45393</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44477</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45075</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45442</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45320</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44841</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>46027</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44882</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45597</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45610</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44475</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45573</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>46038</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44988</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45739</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45519</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>46049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44531</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44901</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45847</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44928</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45919</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>46071</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45562</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45013</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>46101</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45950</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45260</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44977</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45260</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45005</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45069</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45594</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45972</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45055</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45841</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45474</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45103</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45981</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45721</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45583</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46136</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45005</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45013</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45638</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45903</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45094</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>46141</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>46141</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44529</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45077</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45079</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44978</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44930</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45824</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45055</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>46150</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46149</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46149</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46149</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44475</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>46149</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>46149</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>46013</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45835</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44944</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45104</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45562</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46162</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45581</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44489</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44992</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46177</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45040</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>46177</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44944</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46178</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>46055</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45084</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45673</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45324</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44825</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45548</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45223</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45799</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45199</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45104</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>46202</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>46206</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>46206</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44593</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>46251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>46209</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>46209</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44659</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44697</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>46162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>46216</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>46216</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45660</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45442</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46216</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44722</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44726</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45170</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45078</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45163</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45237</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>46269</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46269</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>46210</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45320</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45279</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45098</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44697</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>46136</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>46279</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45212</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>46210</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46281</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44530</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46286</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45562</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>44593</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>46287</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44817</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44993</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>46223</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45161</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44593</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44875</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45581</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45328</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45077</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45544</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45523</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45224</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>44855</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45399</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45751</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45739</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44991</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45579</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45404</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45086</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45211</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45264</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45349</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45554</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44883</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45537</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44599</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44701</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44701</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45209</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44858</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>44936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45348</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45434</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45434</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45558</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45558</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45434</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>44936</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45558</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45109</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44853</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44859</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45579</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45558</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45798</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45947</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46044</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>46210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>46210</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>46210</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45391</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>46199</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45544</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45903</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>46057</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45235</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44858</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>44596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45992</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44633</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45058</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>46288</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46289</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45006</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>46030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45015</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>46000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46218</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45719</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44859</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44697</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44697</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44608</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44782</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44880</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45660</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>45079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45544</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45610</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45519</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45328</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45537</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44928</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44489</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46038</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45086</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45573</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45597</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44531</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45919</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45040</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45958</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>46071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45077</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45950</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44841</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45419</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44991</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45581</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45972</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45638</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45094</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45721</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44817</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45055</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45155</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>45981</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44475</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45224</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45583</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44726</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44477</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45824</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44882</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45835</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45170</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45239</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45055</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45673</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45264</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44992</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44659</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45211</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46136</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46141</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46141</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45320</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44825</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44978</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45594</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45706</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45209</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44616</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46149</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>46149</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46150</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45324</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>46013</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44977</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45237</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46162</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44529</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45799</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45075</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44475</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>46178</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>46055</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45013</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>46202</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45562</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46206</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45078</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44593</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>46209</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46216</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>46216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>44845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45442</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45260</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45013</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45474</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45005</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>44593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45077</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46269</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46269</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46168</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46136</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45098</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46210</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45474</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45579</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45442</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46286</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45055</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46287</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46223</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44875</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44697</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45588</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44530</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44593</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46251</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45404</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44722</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>46253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45714</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45238</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45069</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44697</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45751</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45275</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45393</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44855</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45341</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45005</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45562</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45562</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45320</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45554</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45349</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45209</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44858</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45348</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45434</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45558</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44599</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44701</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45434</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45109</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>44853</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44859</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45579</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45558</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>46210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>46210</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>45391</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>46199</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45544</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44949</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45903</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>46057</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45235</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44858</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44691</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>44596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45992</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44633</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45058</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>46202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>46288</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46289</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45006</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>46030</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45015</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>46000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>46218</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45719</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44859</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44691</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44697</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44697</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44608</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44782</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44880</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45660</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>45079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45544</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44883</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45610</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44930</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45519</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45328</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45537</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45399</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44928</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44489</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46038</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45847</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45086</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45573</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45597</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44531</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45919</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45040</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45958</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>46071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45077</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45950</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44841</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45419</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44991</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45581</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45972</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45638</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45094</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45721</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44817</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45055</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45155</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>45981</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44475</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45224</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45583</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44726</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44477</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45824</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44882</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44812</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45835</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45170</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45239</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45055</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45673</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45264</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44992</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44659</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45211</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46136</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46141</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46141</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45320</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44825</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44978</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45594</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45706</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45209</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44616</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46149</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>46149</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46150</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45324</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>46013</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44977</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45237</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46162</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44529</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45799</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45075</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44475</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>46178</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>46055</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45013</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>46202</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45562</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46206</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45078</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44593</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>46209</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46216</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>46216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>44845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45442</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45260</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45013</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45474</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45005</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>44593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45077</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46269</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46269</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>44855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46168</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46136</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45098</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46210</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45474</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45579</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45442</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46286</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45055</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46287</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46223</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44875</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44992</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44697</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45588</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44530</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44593</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46251</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45404</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44722</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>46253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45714</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45099</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45238</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45069</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44697</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45751</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45275</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45393</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44855</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45341</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45005</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45562</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45562</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45320</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45554</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45349</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45209</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44858</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45348</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45434</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45558</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44599</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44701</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45434</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44701</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45109</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>44853</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44859</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45579</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45558</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>46210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>46210</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46279</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45391</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46199</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>45544</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44949</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45235</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>46057</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44858</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44805</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45335</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44633</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45058</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45992</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46288</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45006</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>46030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45603</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45015</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46055</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>46218</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>46274</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44859</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44691</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44697</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44782</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44825</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44930</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45077</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45324</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45419</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45544</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45523</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45341</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45099</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44855</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45072</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44812</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45562</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45224</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45442</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45075</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45399</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45581</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45751</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44489</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45739</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44991</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45320</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44841</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44882</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44838</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45086</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45040</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45264</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45739</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44944</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45519</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45847</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45673</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>44901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45324</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45349</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45554</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44616</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45919</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44928</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45548</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44883</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>45223</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44609</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45562</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45537</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45199</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45104</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45013</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44817</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45597</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45055</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44722</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44977</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44659</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45894</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45209</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45817</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45260</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45721</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44697</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45005</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45069</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44593</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45660</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45442</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45198</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45055</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44722</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45835</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45583</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45005</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45167</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45013</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45841</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45078</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45785</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45237</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45320</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45098</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44697</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45474</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44880</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44529</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45079</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45538</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45903</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45562</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44936</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44817</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>46136</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46027</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44875</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45328</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46049</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44944</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46141</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46141</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46150</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>46149</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46149</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45958</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>46071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46013</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46178</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>46055</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>46202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>46206</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>46209</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>46209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>46209</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46209</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46162</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46216</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>46216</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46216</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46198</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46265</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>46269</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46269</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46281</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>46287</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>46245</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46251</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46253</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46295</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46162</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46168</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>46223</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>46210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44599</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44701</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45348</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45434</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45434</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45558</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45109</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44853</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44859</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45558</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45947</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46034</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46210</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46279</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45391</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46199</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>45544</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44949</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45235</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>46057</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44858</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44805</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45335</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44633</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45058</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45992</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46288</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45006</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>46030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45603</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45015</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45719</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46055</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>46218</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>46274</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44859</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44691</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44697</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44782</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44825</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44930</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45077</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45324</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45419</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45544</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45523</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45341</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45099</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44855</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45072</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44812</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45562</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45224</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45442</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45075</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45399</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45581</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45751</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44489</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45739</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44991</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45579</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45320</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44841</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45275</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44882</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44838</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45086</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45040</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45264</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45739</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44944</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45084</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45519</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45847</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45673</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>44901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>45324</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45349</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45554</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44616</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45919</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44928</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45548</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44883</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>45223</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44609</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45562</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45537</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45199</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45104</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45013</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44817</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45597</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45055</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44722</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45260</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44977</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44659</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45894</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45209</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45817</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45950</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45260</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45721</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44697</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45005</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45069</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44593</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45660</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45442</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45198</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45055</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>44722</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45835</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45583</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45972</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45005</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45167</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45013</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45841</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45078</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45785</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45237</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45320</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45098</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44697</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45474</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44880</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44529</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45079</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>44978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45538</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45903</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45562</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44936</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44817</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>46136</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46027</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44875</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45328</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46049</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44944</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46141</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46141</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46150</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>46149</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46149</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45958</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>46071</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46013</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>46177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46178</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>46055</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>46202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>46206</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>46209</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>46209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>46209</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46209</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46162</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46216</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>46216</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46216</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46198</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46265</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>46269</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46269</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46281</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>46287</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>46245</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46251</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46253</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46295</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46162</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46168</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>46223</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>46210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44599</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>44701</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44701</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45348</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45434</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45434</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45558</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45109</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44853</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44859</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45558</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45947</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46034</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46044</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46210</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46279</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45391</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46199</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>45544</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44949</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45235</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44858</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44805</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45335</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44633</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45058</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46288</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45006</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>46030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45015</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45217</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44859</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44697</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44691</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44608</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44575</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44782</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44679</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44816</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45660</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44880</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45544</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45328</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45519</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45399</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44489</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45040</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45260</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45077</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45324</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45739</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44991</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45581</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45055</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45155</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45224</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45583</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44726</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44838</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44812</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46141</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45170</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45239</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45055</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45673</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45264</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44992</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45223</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45104</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>46149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46149</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>46149</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45198</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>46013</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45894</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45320</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45548</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>44978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45706</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44944</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45209</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45972</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45538</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45841</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45324</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44977</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45237</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44529</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45903</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45075</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>46027</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44988</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>46177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>46177</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46178</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46055</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45013</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44609</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45958</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>46071</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45739</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45562</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45078</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44593</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45442</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45260</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45005</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44593</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45077</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45098</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44901</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45474</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45579</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46209</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45442</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46216</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>46216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>46198</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45055</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44697</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45588</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45212</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45199</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44593</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46136</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45167</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45072</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44722</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45404</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45163</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44722</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46286</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45714</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45238</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45324</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>46287</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44697</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45751</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45275</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45393</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44855</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45341</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>46251</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45005</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46295</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45562</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45320</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46253</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45554</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45349</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>46168</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45537</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46223</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45573</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44531</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46309</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46265</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45638</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45094</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45721</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46269</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45835</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45785</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45799</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45209</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44858</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45348</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45434</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45434</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45558</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45558</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44599</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44701</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45434</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45558</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44701</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45109</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>44853</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>44859</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45947</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46279</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45391</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>46199</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>45544</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44949</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>45903</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45581</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45235</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>44858</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>44805</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45335</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44633</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45058</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46288</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45006</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>46030</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45015</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46274</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45217</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44859</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44665</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44697</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44691</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44487</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44608</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44575</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44782</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44679</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44816</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45660</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>44880</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45544</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45328</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45519</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45399</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44489</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45040</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45260</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45077</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45324</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45739</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44991</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45581</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45055</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45155</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45224</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45583</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44726</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44838</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44812</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46141</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45170</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45239</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45055</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45673</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45264</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44992</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45223</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45104</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>46149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46149</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>46149</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45198</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>46013</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45894</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45320</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45548</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>44978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45706</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44944</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45209</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45972</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45538</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45841</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45324</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44977</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45237</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44529</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45903</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45075</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>46027</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44988</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>46177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>46177</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46178</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46055</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45013</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44609</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45958</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>46071</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45739</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45562</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45078</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44593</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45442</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45260</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45005</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44593</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45077</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45098</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44901</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45474</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45579</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46209</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>46209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45442</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46216</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>46216</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>46198</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45055</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44697</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45588</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45212</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45199</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44593</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46136</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45167</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45072</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44722</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45404</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45163</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44722</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46286</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45714</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45238</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45324</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>46287</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44697</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45751</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45275</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45393</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44855</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45341</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>46251</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45005</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>46295</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45562</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45320</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46253</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45554</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45349</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>46168</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45537</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46223</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45573</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44531</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46309</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46265</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45638</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45094</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45721</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46269</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45824</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45835</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45785</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45799</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45209</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44858</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45348</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45434</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45434</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45558</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45558</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44599</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44701</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45434</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45558</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>44701</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45109</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>44853</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>44859</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45947</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46057</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45391</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>46199</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,75 +1406,189 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
+          <t>A 37092-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Stor sotdyna
+Sydlig sotticka
+Gulnål
+Bergfink</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37092-2026 artfynd.xlsx", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37092-2026 karta.png", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37092-2026 georefererad karta.tif", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37092-2026 FSC-klagomål.docx", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37092-2026 FSC-klagomål mail.docx", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37092-2026 tillsynsbegäran.docx", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37092-2026 tillsynsbegäran mail.docx", "A 37092-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 37092-2026 prioriterade fågelarter.docx", "A 37092-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>A 37966-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45544</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46319</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsiska
 Röd glada
@@ -1483,111 +1597,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37966-2024 artfynd.xlsx", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37966-2024 karta.png", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37966-2024 georefererad karta.tif", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37966-2024 FSC-klagomål.docx", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37966-2024 FSC-klagomål mail.docx", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37966-2024 tillsynsbegäran.docx", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37966-2024 tillsynsbegäran mail.docx", "A 37966-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 37966-2024 prioriterade fågelarter.docx", "A 37966-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 15788-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46107</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46319</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KLIPPAN</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Entita
 Gulsparv
@@ -1596,149 +1710,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 15788-2026 artfynd.xlsx", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 15788-2026 karta.png", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 15788-2026 georefererad karta.tif", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 15788-2026 FSC-klagomål.docx", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 15788-2026 FSC-klagomål mail.docx", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 15788-2026 tillsynsbegäran.docx", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 15788-2026 tillsynsbegäran mail.docx", "A 15788-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 15788-2026 prioriterade fågelarter.docx", "A 15788-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 37092-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46319</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KLIPPAN</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Vedlavklubba
-Entita
-Stor sotdyna
-Sydlig sotticka
-Gulnål</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/artfynd/A 37092-2026 artfynd.xlsx", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor/A 37092-2026 karta.png", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/kartor_geotiff/A 37092-2026 georefererad karta.tif", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomål/A 37092-2026 FSC-klagomål.docx", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/klagomålsmail/A 37092-2026 FSC-klagomål mail.docx", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsyn/A 37092-2026 tillsynsbegäran.docx", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/tillsynsmail/A 37092-2026 tillsynsbegäran mail.docx", "A 37092-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1276/fåglar/A 37092-2026 prioriterade fågelarter.docx", "A 37092-2026")</f>
         <v/>
       </c>
     </row>
@@ -1762,7 +1763,7 @@
         <v>44949</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1876,7 @@
         <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1988,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2099,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2209,7 +2210,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2325,7 +2326,7 @@
         <v>46289</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2437,7 @@
         <v>45235</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2547,7 +2548,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2658,7 +2659,7 @@
         <v>46309</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2769,7 +2770,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2881,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2991,7 +2992,7 @@
         <v>44858</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3099,7 @@
         <v>44805</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3210,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3316,7 @@
         <v>44596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3426,7 @@
         <v>45335</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3535,7 +3536,7 @@
         <v>46206</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3650,7 +3651,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3756,7 +3757,7 @@
         <v>46202</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3872,7 @@
         <v>45992</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3986,7 +3987,7 @@
         <v>46288</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4096,7 +4097,7 @@
         <v>44633</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4206,7 +4207,7 @@
         <v>45058</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4312,7 +4313,7 @@
         <v>45006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4418,7 +4419,7 @@
         <v>44754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,7 +4525,7 @@
         <v>46030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4630,7 +4631,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4735,7 +4736,7 @@
         <v>46218</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4840,7 +4841,7 @@
         <v>45603</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4945,7 +4946,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5051,7 @@
         <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5164,7 +5165,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5278,7 +5279,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5388,7 +5389,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5493,7 +5494,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5603,7 +5604,7 @@
         <v>46150</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5708,7 +5709,7 @@
         <v>45015</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5817,7 +5818,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5922,7 +5923,7 @@
         <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6027,7 +6028,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6132,7 +6133,7 @@
         <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6237,7 +6238,7 @@
         <v>45217</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6342,7 +6343,7 @@
         <v>44859</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6447,7 +6448,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6526,7 @@
         <v>44883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6603,7 +6604,7 @@
         <v>44596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6681,7 +6682,7 @@
         <v>44691</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6754,7 +6755,7 @@
         <v>44697</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6827,7 +6828,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6900,7 +6901,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6973,7 +6974,7 @@
         <v>44575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7051,7 +7052,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7124,7 +7125,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7202,7 +7203,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7280,7 +7281,7 @@
         <v>44575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7358,7 +7359,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7436,7 +7437,7 @@
         <v>44782</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7509,7 +7510,7 @@
         <v>44825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7587,7 +7588,7 @@
         <v>44880</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7660,7 +7661,7 @@
         <v>44700</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7738,7 +7739,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7811,7 +7812,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7884,7 +7885,7 @@
         <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7957,7 +7958,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8030,7 +8031,7 @@
         <v>45714</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8103,7 +8104,7 @@
         <v>45341</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8176,7 +8177,7 @@
         <v>44993</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8249,7 +8250,7 @@
         <v>45072</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8322,7 +8323,7 @@
         <v>44838</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8400,7 +8401,7 @@
         <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8473,7 +8474,7 @@
         <v>45161</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8546,7 +8547,7 @@
         <v>45905</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8619,7 +8620,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8692,7 +8693,7 @@
         <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8765,7 +8766,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8838,7 +8839,7 @@
         <v>45847</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8911,7 +8912,7 @@
         <v>45581</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8990,7 @@
         <v>45919</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9063,7 @@
         <v>45324</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9140,7 +9141,7 @@
         <v>45328</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9213,7 +9214,7 @@
         <v>45419</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9291,7 +9292,7 @@
         <v>44944</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9364,7 +9365,7 @@
         <v>45077</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9437,7 +9438,7 @@
         <v>44855</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9510,7 +9511,7 @@
         <v>46177</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9583,7 +9584,7 @@
         <v>45239</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9656,7 +9657,7 @@
         <v>44812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9729,7 +9730,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9802,7 +9803,7 @@
         <v>45393</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9875,7 +9876,7 @@
         <v>45894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9948,7 +9949,7 @@
         <v>45442</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10021,7 +10022,7 @@
         <v>45075</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10094,7 +10095,7 @@
         <v>45950</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10167,7 +10168,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10240,7 +10241,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10313,7 +10314,7 @@
         <v>46055</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10386,7 +10387,7 @@
         <v>45523</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10459,7 +10460,7 @@
         <v>45224</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10532,7 +10533,7 @@
         <v>44855</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10605,7 +10606,7 @@
         <v>45399</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10683,7 +10684,7 @@
         <v>45972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10756,7 +10757,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10829,7 +10830,7 @@
         <v>45739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10902,7 +10903,7 @@
         <v>44991</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10975,7 +10976,7 @@
         <v>45579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11048,7 +11049,7 @@
         <v>45841</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11121,7 +11122,7 @@
         <v>46202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11194,7 +11195,7 @@
         <v>45404</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11272,7 +11273,7 @@
         <v>46206</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11350,7 +11351,7 @@
         <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11428,7 +11429,7 @@
         <v>46209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11506,7 +11507,7 @@
         <v>45086</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11579,7 +11580,7 @@
         <v>46209</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11657,7 +11658,7 @@
         <v>46209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11735,7 +11736,7 @@
         <v>45211</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11808,7 +11809,7 @@
         <v>45320</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11881,7 +11882,7 @@
         <v>46162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11954,7 +11955,7 @@
         <v>46216</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12027,7 +12028,7 @@
         <v>46216</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12100,7 +12101,7 @@
         <v>46216</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12173,7 +12174,7 @@
         <v>46198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12251,7 +12252,7 @@
         <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12324,7 +12325,7 @@
         <v>45903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12397,7 +12398,7 @@
         <v>45349</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12475,7 +12476,7 @@
         <v>45554</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12553,7 +12554,7 @@
         <v>46136</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12631,7 +12632,7 @@
         <v>46281</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12704,7 +12705,7 @@
         <v>44841</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12777,7 +12778,7 @@
         <v>45946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12850,7 +12851,7 @@
         <v>46027</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12923,7 +12924,7 @@
         <v>44883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13001,7 +13002,7 @@
         <v>45537</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13074,7 +13075,7 @@
         <v>46286</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13147,7 +13148,7 @@
         <v>46287</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13220,7 +13221,7 @@
         <v>46245</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13293,7 +13294,7 @@
         <v>45597</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13366,7 +13367,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13439,7 +13440,7 @@
         <v>46049</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13512,7 +13513,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13590,7 +13591,7 @@
         <v>44882</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13663,7 +13664,7 @@
         <v>44845</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13736,7 +13737,7 @@
         <v>45817</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13809,7 +13810,7 @@
         <v>45721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13882,7 +13883,7 @@
         <v>45638</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13955,7 +13956,7 @@
         <v>45094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14028,7 +14029,7 @@
         <v>45958</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14101,7 +14102,7 @@
         <v>46071</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14174,7 +14175,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14247,7 +14248,7 @@
         <v>46251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14320,7 +14321,7 @@
         <v>46253</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14393,7 +14394,7 @@
         <v>46295</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14466,7 +14467,7 @@
         <v>45824</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14539,7 +14540,7 @@
         <v>45835</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14612,7 +14613,7 @@
         <v>46162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14685,7 +14686,7 @@
         <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14758,7 +14759,7 @@
         <v>45785</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14831,7 +14832,7 @@
         <v>46223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14904,7 +14905,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14977,7 +14978,7 @@
         <v>44988</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15050,7 +15051,7 @@
         <v>46265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15123,7 +15124,7 @@
         <v>45739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15196,7 +15197,7 @@
         <v>45519</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15274,7 +15275,7 @@
         <v>46136</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15352,7 +15353,7 @@
         <v>46210</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15430,7 +15431,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15508,7 +15509,7 @@
         <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15581,7 +15582,7 @@
         <v>46269</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15654,7 +15655,7 @@
         <v>46000</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15732,7 +15733,7 @@
         <v>44609</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15805,7 +15806,7 @@
         <v>46316</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15878,7 +15879,7 @@
         <v>45562</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15956,7 +15957,7 @@
         <v>46315</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16029,7 +16030,7 @@
         <v>45013</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16102,7 +16103,7 @@
         <v>46317</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16175,7 +16176,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16248,7 +16249,7 @@
         <v>46141</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16321,7 +16322,7 @@
         <v>45055</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16394,7 +16395,7 @@
         <v>46150</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16467,7 +16468,7 @@
         <v>46149</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16540,7 +16541,7 @@
         <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16613,7 +16614,7 @@
         <v>46149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16686,7 +16687,7 @@
         <v>46149</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16759,7 +16760,7 @@
         <v>44722</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16832,7 +16833,7 @@
         <v>46013</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16905,7 +16906,7 @@
         <v>45260</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16978,7 +16979,7 @@
         <v>44977</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17051,7 +17052,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17124,7 +17125,7 @@
         <v>45005</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17202,7 +17203,7 @@
         <v>45069</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17275,7 +17276,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17348,7 +17349,7 @@
         <v>45055</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17421,7 +17422,7 @@
         <v>45238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17494,7 +17495,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17567,7 +17568,7 @@
         <v>45103</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17640,7 +17641,7 @@
         <v>45583</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17713,7 +17714,7 @@
         <v>45005</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17791,7 +17792,7 @@
         <v>45013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17864,7 +17865,7 @@
         <v>44529</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17937,7 +17938,7 @@
         <v>45077</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18010,7 +18011,7 @@
         <v>45079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18083,7 +18084,7 @@
         <v>44978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18156,7 +18157,7 @@
         <v>45538</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18234,7 +18235,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18307,7 +18308,7 @@
         <v>45055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18380,7 +18381,7 @@
         <v>45588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18453,7 +18454,7 @@
         <v>45099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18526,7 +18527,7 @@
         <v>44944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18604,7 +18605,7 @@
         <v>45104</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18677,7 +18678,7 @@
         <v>45562</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18755,7 +18756,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18833,7 +18834,7 @@
         <v>45275</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18906,7 +18907,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18984,7 +18985,7 @@
         <v>44992</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19057,7 +19058,7 @@
         <v>45040</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19130,7 +19131,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19203,7 +19204,7 @@
         <v>45084</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19281,7 +19282,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19354,7 +19355,7 @@
         <v>45673</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19427,7 +19428,7 @@
         <v>45324</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19500,7 +19501,7 @@
         <v>44825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19573,7 +19574,7 @@
         <v>44616</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19646,7 +19647,7 @@
         <v>45548</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19719,7 +19720,7 @@
         <v>45223</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19792,7 +19793,7 @@
         <v>45199</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19865,7 +19866,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19938,7 +19939,7 @@
         <v>44817</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20011,7 +20012,7 @@
         <v>44593</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20084,7 +20085,7 @@
         <v>44659</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20157,7 +20158,7 @@
         <v>45209</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20230,7 +20231,7 @@
         <v>44697</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20303,7 +20304,7 @@
         <v>44593</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20376,7 +20377,7 @@
         <v>45660</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20449,7 +20450,7 @@
         <v>45442</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20522,7 +20523,7 @@
         <v>45198</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20595,7 +20596,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20668,7 +20669,7 @@
         <v>45163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20741,7 +20742,7 @@
         <v>44726</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20814,7 +20815,7 @@
         <v>45170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20887,7 +20888,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20960,7 +20961,7 @@
         <v>45167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21033,7 +21034,7 @@
         <v>45078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21106,7 +21107,7 @@
         <v>45163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21179,7 +21180,7 @@
         <v>45237</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21252,7 +21253,7 @@
         <v>45320</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21325,7 +21326,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21398,7 +21399,7 @@
         <v>45098</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21471,7 +21472,7 @@
         <v>44697</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21544,7 +21545,7 @@
         <v>45212</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21617,7 +21618,7 @@
         <v>45474</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21690,7 +21691,7 @@
         <v>44880</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21763,7 +21764,7 @@
         <v>44530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21836,7 +21837,7 @@
         <v>45562</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21914,7 +21915,7 @@
         <v>44593</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21987,7 +21988,7 @@
         <v>44936</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22060,7 +22061,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22133,7 +22134,7 @@
         <v>44701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22206,7 +22207,7 @@
         <v>44701</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22279,7 +22280,7 @@
         <v>45209</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22352,7 +22353,7 @@
         <v>44858</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22425,7 +22426,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22498,7 +22499,7 @@
         <v>45348</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22571,7 +22572,7 @@
         <v>45434</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22649,7 +22650,7 @@
         <v>45434</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22727,7 +22728,7 @@
         <v>45558</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22805,7 +22806,7 @@
         <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22883,7 +22884,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22961,7 +22962,7 @@
         <v>44936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23034,7 +23035,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23112,7 +23113,7 @@
         <v>45109</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23185,7 +23186,7 @@
         <v>44853</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23258,7 +23259,7 @@
         <v>44859</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23331,7 +23332,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23404,7 +23405,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23482,7 +23483,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23555,7 +23556,7 @@
         <v>45947</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23628,7 +23629,7 @@
         <v>46034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23701,7 +23702,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23779,7 +23780,7 @@
         <v>46210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23857,7 +23858,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23935,7 +23936,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>

--- a/Översikt KLIPPAN.xlsx
+++ b/Översikt KLIPPAN.xlsx
@@ -601,7 +601,7 @@
         <v>45314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45960</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46057</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45391</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>46199</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>45544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46107</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>44949</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>45919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>46289</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45235</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>46309</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>44858</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44805</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45335</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46206</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>46202</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45992</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>46288</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>44633</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45058</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>46030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>46218</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45603</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>46150</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45015</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45719</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>44665</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45217</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>44859</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44691</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44697</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44697</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44782</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44880</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44700</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45714</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45341</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44993</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45072</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>44838</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>45161</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45905</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45847</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45581</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45919</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45324</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45328</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45419</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44944</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45077</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>44855</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>46177</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45239</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45393</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45442</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45075</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45950</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>46055</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45523</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45224</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44855</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45399</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44991</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45841</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>46202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45404</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>46206</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>46209</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45086</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>46209</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>46209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45211</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45320</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>46162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>46216</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>46216</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>46216</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>46198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45349</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45554</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>46136</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>46281</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44841</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>45946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>46027</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45537</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>46286</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>46287</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>46245</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45597</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>46049</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>44882</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44845</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45817</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45638</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45958</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>46071</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>46251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>46253</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>46295</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45824</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45835</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>46162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45785</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44988</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45519</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>46136</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>46210</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>46269</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46000</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44609</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>46316</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45562</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>46315</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45013</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46317</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>46141</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45055</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>46150</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>46149</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>46149</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44722</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>46013</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45260</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44977</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45005</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45069</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45055</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45103</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45583</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45005</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>44529</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45077</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45538</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45104</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45562</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45275</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>44992</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45040</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45084</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45673</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45324</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>44616</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45548</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45223</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45199</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>44817</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44593</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44659</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45209</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>44697</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>44593</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45660</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45442</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45198</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>44726</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45237</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45320</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45098</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44697</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45212</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45474</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44880</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45562</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>44593</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44936</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44701</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45209</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44858</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45348</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45434</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45434</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45558</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>44936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45109</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44853</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44859</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45558</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45947</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46034</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
